--- a/assets/docs/lop4/KHDH ca khoi - Lop 4.xlsx
+++ b/assets/docs/lop4/KHDH ca khoi - Lop 4.xlsx
@@ -696,7 +696,12 @@
           <t>4+5</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu văn bản “Thi nhạc” lên tivi, bật bản đọc mẫu diễn cảm và chiếu tranh minh hoạ tiết mục của ve sầu, gà trống, dế mèn, hoạ mi; HS nghe
+Năng lực số Miền 3 (Cơ bản, bậc 2): Sau khi luyện đọc, GV dùng điện thoại ghi âm nhóm HS đọc phân vai các tiết mục trong câu chuyện, phát lại qua loa; lớp nghe</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -941,7 +946,12 @@
           <t>11+12</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Khởi động bài “Công chúa và người dẫn chuyện”, GV chiếu ảnh các loài hoa như hồng, sen, cúc, hướng dương lên tivi để HS chọn một loài
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần tìm hiểu bài, GV chiếu bảng hai cột lời nói và suy nghĩ của Giét-xi trước và sau khi trò chuyện với cô giáo; nhóm thảo luận</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1067,7 +1077,8 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Trước khi đọc bài “Thằn lằn xanh và tắc kè”, GV chiếu ảnh thật hai con vật này.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước khi đọc bài “Thằn lằn xanh và tắc kè”, GV chiếu ảnh thật hai con vật này cùng nơi chúng sống để HS phân biệt được hai nhân vật; trong lúc luyện đọc
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt đọc diễn cảm của một vài HS rồi mở lại cho cả lớp nghe; các em đối chiếu với hai tiêu chí chiếu sẵn là nhấn giọng đúng từ ngữ…</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1199,12 @@
           <t>18+19</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Nghệ sĩ trống”, GV mở một đoạn nhạc độc tấu và ảnh một số nhạc cụ để HS nhận ra âm sắc của trống giữa các nhạc cụ khác
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt đọc diễn cảm phần miêu tả tiết mục của từng nhóm rồi mở lại; HS nghe và nhận xét theo tiêu chí đọc rõ, nhấn đúng từ tả âm thanh</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1313,7 +1329,8 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 2): Ghi âm lượt đọc diễn cảm của một vài.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Những bức chân dung”, GV chiếu tranh minh hoạ phóng to để HS đoán tên thân mật của các nhân vật; trong lúc luyện đọc
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt đọc diễn cảm của một vài HS rồi mở lại cho cả lớp nghe; các em đối chiếu với hai tiêu chí chiếu sẵn là nhấn đúng từ gợi tả…</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1455,12 @@
           <t>25+26</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Đò ngang”, GV chiếu ảnh thật một bến đò, một chiếc thuyền mành đi biển và một con đò ngang chở khách qua sông
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt đọc phân vai lời thuyền ngang và thuyền mành rồi mở lại; HS nghe và nhận xét theo tiêu chí phân biệt được lời người dẫn chuyện với lời từng…</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -1564,7 +1586,8 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Trước bài đọc “Bầu trời trong quả trứng”, GV chiếu tranh minh hoạ phóng to.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Bầu trời trong quả trứng”, GV chiếu tranh minh hoạ phóng to cùng vài ảnh gà con mới nở
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt đọc diễn cảm bài thơ của một vài HS rồi mở lại cho cả lớp nghe; các em đối chiếu với tiêu chí chiếu sẵn là ngắt nhịp đúng và…</t>
         </is>
       </c>
     </row>
@@ -1685,7 +1708,12 @@
           <t>32+33</t>
         </is>
       </c>
-      <c r="H31" s="4" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Tiếng nói của cỏ cây”, GV chiếu một đoạn phim tua nhanh cảnh hạt nảy mầm và cây lớn lên từng ngày; HS thấy được cây cũng thay đổi
+Năng lực số Miền 3 (Cơ bản, bậc 2): GV hướng dẫn HS lập một bảng theo dõi cây trên máy hoặc trong vở gồm ngày, chiều cao, số lá, ghi chú</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -1809,7 +1837,8 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 2): Ghi âm lượt đọc diễn cảm của một vài.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Tập làm văn”, GV chiếu tranh minh hoạ phóng to để HS đoán nội dung, sau đó chiếu đoạn văn và tô màu những chi tiết cho thấy nhân vật đã…
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt đọc diễn cảm của một vài HS rồi mở lại cho cả lớp nghe; các em đối chiếu với tiêu chí chiếu sẵn là đọc rõ lời nhân vật và…</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2084,8 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Trước bài đọc “Con vẹt xanh”, GV chiếu ảnh và một đoạn phim ngắn về con vẹt biết nhại tiếng người.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Con vẹt xanh”, GV chiếu ảnh và một đoạn phim ngắn về con vẹt biết nhại tiếng người; HS nói được vẹt chỉ bắt chước âm thanh nghe được
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt đọc phân vai của một nhóm rồi mở lại cho cả lớp nghe; các em nhận xét theo tiêu chí chiếu sẵn là phân biệt được lời người kể với…</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2205,12 @@
           <t>46+47</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Chân trời cuối phố”, GV chiếu ảnh một con phố nhìn từ nhiều phía và ảnh khoảng trời cuối phố lúc hoàng hôn; HS nói cảm nhận của mình
+Năng lực số Miền 3 (Cơ bản, bậc 2): Sau khi đọc, mỗi nhóm chọn một câu văn tả cảnh trong bài rồi vẽ hoặc chọn ảnh minh hoạ, viết một câu nêu cảm nghĩ</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -2424,7 +2459,12 @@
           <t>53+54</t>
         </is>
       </c>
-      <c r="H49" s="4" t="inlineStr"/>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Trước ngày xa quê”, GV chiếu ảnh những hình ảnh thân thuộc của làng quê như bến sông, cánh đồng, con đường làng
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt đọc diễn cảm của vài HS rồi mở lại cho cả lớp nghe; các em đối chiếu với tiêu chí chiếu sẵn là ngắt nghỉ đúng và giọng đọc thể…</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -2617,7 +2657,8 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 2): Ghi âm lượt đọc diễn cảm của vài.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Vẽ màu”, GV chiếu bảng màu và vài bức tranh có gam màu khác nhau, phóng to từng mảng; HS gọi tên màu, nói cảm giác mà mỗi màu gợi ra
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt đọc diễn cảm của vài HS rồi mở lại cho cả lớp nghe; các em đối chiếu với tiêu chí chiếu sẵn là ngắt nhịp thơ đúng và giọng đọc…</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2779,12 @@
           <t>67+68</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr"/>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Đồng cỏ nở hoa”, GV chiếu một đoạn phim ngắn giới thiệu hoạ sĩ Tô Ngọc Vân và vài bức tranh của ông
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt đọc diễn cảm của một nhóm rồi mở lại; cả lớp nhận xét theo tiêu chí chiếu sẵn là đọc rõ lời nhân vật và thể hiện được sự hồn…</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -2983,7 +3029,12 @@
           <t>74+75</t>
         </is>
       </c>
-      <c r="H63" s="4" t="inlineStr"/>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Bầu trời mùa thu”, GV chiếu chùm ảnh bầu trời ở các thời điểm khác nhau trong ngày và trong năm; HS so sánh màu sắc
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt đọc diễn cảm của vài HS rồi mở lại cho cả lớp nghe; các em đối chiếu với tiêu chí chiếu sẵn là ngắt nghỉ đúng và giọng đọc thể…</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -3105,7 +3156,8 @@
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Chiếu các bước gấp bị đảo lộn thứ tự cho HS sắp lại cho đúng.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Làm thỏ con bằng giấy”, GV chiếu đoạn phim hướng dẫn gấp giấy, cho chạy chậm và dừng ở mỗi nếp gấp
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV chiếu các bước gấp bị đảo lộn thứ tự cho HS sắp lại cho đúng; máy báo đúng, sai ngay nên các em nhận ra bước nào bắt buộc phải làm trước rồi…</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3277,12 @@
           <t>81+82</t>
         </is>
       </c>
-      <c r="H69" s="4" t="inlineStr"/>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Bức tường có nhiều phép lạ”, GV chiếu tranh minh hoạ phóng to để HS đoán phép lạ trong bài; trong lúc luyện đọc
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt đọc diễn cảm của vài HS rồi mở lại cho cả lớp nghe; các em đối chiếu với tiêu chí chiếu sẵn là đọc rõ lời nhân vật và thể…</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -3594,7 +3651,8 @@
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 2): Ghi âm lượt đọc diễn cảm của vài.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Bay cùng ước mơ”, GV chiếu tranh minh hoạ phóng to và vài hình ảnh nghề nghiệp mà trẻ em thường mơ ước
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt đọc diễn cảm của vài HS rồi mở lại cho cả lớp nghe; các em đối chiếu với tiêu chí chiếu sẵn là ngắt nghỉ đúng và giọng đọc thể…</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3773,12 @@
           <t>95+96</t>
         </is>
       </c>
-      <c r="H81" s="4" t="inlineStr"/>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trước bài đọc “Con trai người làm vườn”, GV chiếu tranh khởi động phóng to và ảnh một vườn cây đang được chăm sóc; HS nói công việc của người làm vườn
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt đọc phân vai của một nhóm rồi mở lại; cả lớp nhận xét theo tiêu chí chiếu sẵn là phân biệt được lời người kể với lời nhân vật và…</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="inlineStr">
@@ -3839,7 +3902,8 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Đọc đúng bài “Nếu em có một khu vườn”, GV chiếu văn bản lên màn hình.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Đọc đúng bài “Nếu em có một khu vườn”, GV chiếu văn bản lên màn hình, tô sáng những từ ngữ gợi tả cần nhấn giọng và mở bản đọc mẫu…
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở hoạt động Luyện tập, GV mở bài tập tương tác về từ ngữ trong bài: máy hiện câu còn trống, HS chọn từ gợi tả phù hợp rồi bấm kiểm tra</t>
         </is>
       </c>
     </row>
@@ -3964,7 +4028,12 @@
           <t>102+103</t>
         </is>
       </c>
-      <c r="H87" s="4" t="inlineStr"/>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Đọc đúng bài thơ “Bốn mùa mơ ước”, GV chiếu bài thơ lên màn hình, tô sáng những từ ngữ thể hiện cảm xúc về ước mơ và mở bản đọc…
+Năng lực số Miền 3 (Cơ bản, bậc 2): Ở hoạt động Luyện đọc diễn cảm, GV ghi âm phần đọc của vài nhóm rồi mở lại cho cả lớp nghe</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="inlineStr">
@@ -4089,7 +4158,8 @@
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 2): Ở hoạt động Luyện đọc phân vai, GV chiếu bảng phân vai chung lên màn hình.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Đọc đúng vở kịch “Ở vương quốc Tương Lai”, GV chiếu văn bản lên màn hình, tô màu riêng tên nhân vật và lời nhân vật để HS thấy rõ chỗ…
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động Luyện đọc phân vai, GV chiếu bảng phân vai chung lên màn hình; các nhóm đăng kí vai, ghi tên vào bảng rồi đọc theo nhóm</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4284,12 @@
           <t>109+110</t>
         </is>
       </c>
-      <c r="H93" s="4" t="inlineStr"/>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Đọc đúng bài “Cánh chim nhỏ”, GV chiếu văn bản lên màn hình, tô sáng các từ ngữ gợi tả sự vật
+Năng lực số Miền 3 (Cơ bản, bậc 2): Ở hoạt động Luyện đọc diễn cảm, GV ghi âm phần đọc của vài nhóm rồi mở lại; các em đối chiếu với bản đọc mẫu</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="inlineStr">
@@ -4339,7 +4414,8 @@
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Đọc đúng bài thơ “Nếu chúng mình có phép lạ”, GV chiếu bài thơ lên màn hình.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Đọc đúng bài thơ “Nếu chúng mình có phép lạ”, GV chiếu bài thơ lên màn hình, tô sáng những từ ngữ thể hiện mơ ước cần nhấn giọng và mở…
+Năng lực số Miền 3 (Cơ bản, bậc 2): Ở hoạt động Luyện tập, GV mở bảng chung trên máy tính lớp, mỗi nhóm gõ một câu về điều ước của mình theo mẫu câu trong bài rồi chiếu lên; cả lớp đọc</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4536,12 @@
           <t>116+117</t>
         </is>
       </c>
-      <c r="H99" s="4" t="inlineStr"/>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Khởi động và Đọc đúng bài “Anh Ba”, GV chiếu ảnh tư liệu bến Nhà Rồng và con tàu năm 1911 kèm chú thích nguồn
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động Đọc hiểu, GV chiếu bảng chung “Chi tiết trong bài – Điều nói lên ở anh Ba”; các nhóm đọc thầm, tìm chi tiết rồi lên điền</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
@@ -9721,7 +9802,8 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu video kĩ thuật đi đều vòng bên phải trên tivi ở phần hình thành kiến thức của bài “Đi đều vòng bên phải (Tiết 2)”, tua chậm đoạn chuyển hướng
+KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
     </row>
@@ -9998,7 +10080,9 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu video mẫu động tác chân với vòng của chủ đề Bài tập thể dục, cho chạy chậm và dừng hình ở nhịp khuỵu gối và nhịp đưa vòng
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV quay một lượt tập của từng tổ rồi chiếu lại; HS tự chấm theo ba tiêu chí chiếu sẵn là đúng nhịp, đủ biên độ, giữ vòng chắc
+KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
     </row>
@@ -10101,7 +10185,8 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Quay một lượt tập của từng tổ.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu video mẫu động tác nhảy và động tác điều hoà với vòng, cho chạy chậm và dừng hình ở nhịp bật nhảy, nhịp thả lỏng
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV quay một lượt tập của từng tổ rồi chiếu lại; HS tự chấm theo tiêu chí chiếu sẵn là bật đúng nhịp, tiếp đất êm, thả lỏng đủ chậm
 KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
@@ -10203,7 +10288,12 @@
           <t>16</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu video mẫu động tác chân với vòng của chủ đề Bài tập thể dục, cho chạy chậm và dừng hình ở nhịp khuỵu gối và nhịp đưa vòng
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV quay một lượt tập của từng tổ rồi chiếu lại; HS tự chấm theo ba tiêu chí chiếu sẵn là đúng nhịp, đủ biên độ, giữ vòng chắc</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -10267,7 +10357,12 @@
           <t>18</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu video mẫu động tác toàn thân với vòng, cho chạy chậm và dừng hình ở nhịp gập thân, nhịp bật nhảy để HS thấy rõ trình tự phối hợp tay, thân, chân
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV quay một lượt tập của từng tổ rồi chiếu lại; HS tự chấm theo tiêu chí chiếu sẵn là đúng trình tự, đủ biên độ, giữ nhịp chung</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -10331,7 +10426,12 @@
           <t>20</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu video mẫu động tác nhảy và động tác điều hoà với vòng, cho chạy chậm và dừng hình ở nhịp bật nhảy, nhịp thả lỏng
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV quay một lượt tập của từng tổ rồi chiếu lại; HS tự chấm theo tiêu chí chiếu sẵn là bật đúng nhịp, tiếp đất êm, thả lỏng đủ chậm</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -10466,7 +10566,9 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức bài ôn và nâng cao bài tập thăng bằng, GV chiếu trên tivi video kĩ thuật, cho chạy chậm và dừng ở tư thế dang tay
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay lượt tập của vài HS rồi chiếu chậm; cả nhóm cùng chỉ ra lỗi hay gặp như cúi đầu nhìn chân, tay buông xuôi
+KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -10500,7 +10602,8 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Chiếu clip mẫu “Động tác tại chỗ dẫn bóng” và giao cho mỗi tổ một việc quan sát riêng.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần bài tập bổ trợ thăng bằng, GV chiếu trên tivi sơ đồ sân chơi nhìn từ trên xuống kèm mũi tên chỉ đường di chuyển của từng đội
+Năng lực số Miền 5 (Cơ bản, bậc 2): Sau mỗi lượt chơi, GV chiếu bảng kết quả các đội lên tivi kèm số lần mất thăng bằng; các nhóm nhìn bảng để tìm ra mình hay ngã ở đoạn nào và bàn…
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -10709,7 +10812,9 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần bài tập bổ trợ bật xa, GV chiếu trên tivi video kĩ thuật, cho chạy chậm và dừng ở chỗ khuỵu gối lấy đà, đánh tay và tiếp đất bằng hai chân
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV chiếu bảng thành tích bật xa của các nhóm lên tivi sau mỗi lượt; các nhóm nhìn bảng để thấy mình tiến bộ bao nhiêu và bàn cách lấy…
+KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -10949,7 +11054,9 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức bài ôn và nâng cao bài tập thăng bằng, GV chiếu trên tivi video kĩ thuật, cho chạy chậm và dừng ở tư thế dang tay
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay lượt tập của vài HS rồi chiếu chậm; cả nhóm cùng chỉ ra lỗi hay gặp như cúi đầu nhìn chân, tay buông xuôi
+KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -10983,7 +11090,8 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>AI-NB (Nhận biết): Dùng ứng dụng quay chậm có vạch chuẩn.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần bài tập bổ trợ bật xa, GV chiếu trên tivi video kĩ thuật, cho chạy chậm và dừng ở chỗ khuỵu gối lấy đà, đánh tay và tiếp đất bằng hai chân
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV chiếu bảng thành tích bật xa của các nhóm lên tivi sau mỗi lượt; các nhóm nhìn bảng để thấy mình tiến bộ bao nhiêu và bàn cách lấy…
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -11157,7 +11265,9 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức bài ôn và nâng cao bài tập thăng bằng, GV chiếu trên tivi video kĩ thuật, cho chạy chậm và dừng ở tư thế dang tay
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay lượt tập của vài HS rồi chiếu chậm; cả nhóm cùng chỉ ra lỗi hay gặp như cúi đầu nhìn chân, tay buông xuôi
+KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -11191,7 +11301,8 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Sau mỗi lượt chơi, GV chiếu bảng kết quả các đội lên tivi.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần bài tập bổ trợ thăng bằng, GV chiếu trên tivi sơ đồ sân chơi nhìn từ trên xuống kèm mũi tên chỉ đường di chuyển của từng đội
+Năng lực số Miền 5 (Cơ bản, bậc 2): Sau mỗi lượt chơi, GV chiếu bảng kết quả các đội lên tivi kèm số lần mất thăng bằng; các nhóm nhìn bảng để tìm ra mình hay ngã ở đoạn nào và bàn…
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -11296,7 +11407,9 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần bài tập bổ trợ bật xa, GV chiếu trên tivi video kĩ thuật, cho chạy chậm và dừng ở chỗ khuỵu gối lấy đà, đánh tay và tiếp đất bằng hai chân
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV chiếu bảng thành tích bật xa của các nhóm lên tivi sau mỗi lượt; các nhóm nhìn bảng để thấy mình tiến bộ bao nhiêu và bàn cách lấy…
+KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -11426,7 +11539,12 @@
           <t>52</t>
         </is>
       </c>
-      <c r="H55" s="4" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức bài “Ôn bật cao, bật cao có đà ngắn”, GV chiếu trên tivi video kĩ thuật, cho chạy chậm và dừng ở chỗ lấy đà
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV chiếu bảng thành tích bật cao của các nhóm sau mỗi lượt; các nhóm nhìn bảng thấy mình tiến bộ bao nhiêu rồi bàn cách lấy đà ngắn hơn</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -11458,7 +11576,8 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Sau mỗi lượt, GV chiếu bảng kết quả các đội.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần bài tập bổ trợ sức bật, GV chiếu trên tivi sơ đồ sân chơi kèm mũi tên chỉ đường di chuyển và vạch bật của từng đội
+Năng lực số Miền 5 (Cơ bản, bậc 2): Sau mỗi lượt, GV chiếu bảng kết quả các đội kèm số lần bật chưa qua vạch; các nhóm nhìn bảng tìm ra mình yếu ở khâu lấy đà hay khâu vươn người rồi…</t>
         </is>
       </c>
     </row>
@@ -17402,7 +17521,12 @@
           <t>52</t>
         </is>
       </c>
-      <c r="H55" s="4" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài phép cộng các số có nhiều chữ số, GV chiếu bảng hàng phóng to rồi bấm hiện dần từng bước cộng từ hàng đơn vị sang hàng nghìn
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác đặt tính rồi tính với số có nhiều chữ số; máy chấm ngay và chỉ chỗ sai nên HS nhận ra mình viết lệch hàng hay quên nhớ</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -17460,7 +17584,8 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Mở bài tập tương tác đặt tính.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Mở đầu bài phép trừ các số có nhiều chữ số, GV chiếu số lượt xem của hai đoạn phim thiếu nhi lên màn hình; HS đọc đúng số có sáu chữ số
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác đặt tính rồi tính phép trừ có nhớ nhiều lần; máy chấm ngay và chỉ chỗ sai nên HS nhận ra mình quên trả phần đã mượn hay…</t>
         </is>
       </c>
     </row>
@@ -17520,7 +17645,8 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS nêu được các bước giải và nhận ra cấu trúc bài toán không đổi khi số liệu thay đổi.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài tính chất giao hoán và kết hợp của phép cộng, GV chiếu bảng số liệu rồi bấm đổi chỗ hai số hạng, đổi cách nhóm các số
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV chiếu các dãy tính dài rồi cho HS chọn cách nhóm số sao cho tính nhanh nhất; máy báo đúng</t>
         </is>
       </c>
     </row>
@@ -17836,7 +17962,8 @@
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS mô tả được đặc điểm góc, đường thẳng, hình học nhờ quan sát hình động và kiểm chứng bằng dụng cụ vẽ.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài thực hành vẽ hai đường thẳng vuông góc, GV dùng phần mềm hình học chiếu từng bước vẽ: đặt ê ke trùng đường thẳng cho trước, kẻ theo cạnh vuông góc
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV chiếu vài hình vẽ có lỗi như đặt ê ke lệch, kẻ chưa qua điểm cho trước; HS chỉ ra lỗi</t>
         </is>
       </c>
     </row>
@@ -17964,7 +18091,8 @@
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS mô tả được đặc điểm góc, đường thẳng, hình học nhờ quan sát hình động và kiểm chứng bằng dụng cụ vẽ.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động hướng dẫn vẽ của bài “Thực hành vẽ hai đường thẳng song song”, GV chiếu hình động các thao tác đặt ê ke và thước kẻ để vẽ đường thẳng CD…
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở hoạt động Vận dụng, GV chiếu hình có sẵn các cặp cạnh, HS dự đoán cặp nào song song rồi kiểm tra lại bằng ê ke trên vở</t>
         </is>
       </c>
     </row>
@@ -18624,7 +18752,8 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Khám phá bài “Nhân với số có một chữ số”, GV chiếu phép nhân đặt tính dọc lên màn.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Khám phá bài “Nhân với số có một chữ số”, GV chiếu phép nhân đặt tính dọc lên màn hình và cho hiện dần từng lượt nhân, nhớ
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở hoạt động Luyện tập, GV mở bài tập tương tác: HS đặt tính và tính ra vở trước rồi nhập kết quả vào máy; khi máy báo sai</t>
         </is>
       </c>
     </row>
@@ -18684,7 +18813,8 @@
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Ở hoạt động Luyện tập, GV mở bài tập tương tác.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Khám phá bài “Chia cho số có một chữ số”, GV chiếu phép chia đặt tính lên màn hình và cho hiện dần từng lượt chia, nhân, trừ
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở hoạt động Luyện tập, GV mở bài tập tương tác: HS đặt tính và tính ra vở trước rồi nhập kết quả vào máy; khi máy báo sai</t>
         </is>
       </c>
     </row>
@@ -18742,7 +18872,12 @@
           <t>95</t>
         </is>
       </c>
-      <c r="H98" s="4" t="inlineStr"/>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Khám phá bài “Tính chất giao hoán và kết hợp của phép nhân”, GV chiếu bảng hai cột giá trị lên màn hình rồi cho máy tính lần lượt a ×…
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở hoạt động Luyện tập, GV chiếu các biểu thức dài, HS chọn cách nhóm thừa số cho tính nhẩm nhanh nhất rồi bấm kiểm tra</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
@@ -18826,7 +18961,8 @@
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Hình thành kiến thức bài “Nhân, chia với 10, 100, 1 000”, GV chiếu bảng các phép tính 36.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Hình thành kiến thức bài “Nhân, chia với 10, 100, 1 000”, GV chiếu bảng các phép tính 36 × 10, 36 × 100
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở hoạt động Luyện tập, GV mở bài tập tương tác tính nhẩm: HS nhẩm rồi nhập kết quả, máy báo sai thì các em nhìn lại bảng đã tô màu để đếm đúng…</t>
         </is>
       </c>
     </row>
@@ -18884,7 +19020,12 @@
           <t>100</t>
         </is>
       </c>
-      <c r="H103" s="4" t="inlineStr"/>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Hình thành kiến thức bài “Tính chất phân phối của phép nhân đối với phép cộng”, GV chiếu hình đội đồng diễn xếp thành các hàng rồi cho hiện hai cách…
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở hoạt động Luyện tập, GV chiếu các biểu thức, HS chọn cách tính nhanh hơn rồi bấm kiểm tra; máy hiện kết quả cả hai cách để các em so sánh và giải…</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="inlineStr">
@@ -18972,7 +19113,8 @@
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Ở hoạt động Luyện tập, GV mở bài tập tương tác.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Hình thành kiến thức bài “Nhân số có hai chữ số”, GV chiếu phép nhân đặt tính dọc lên màn hình và cho hiện dần từng tích riêng
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở hoạt động Luyện tập, GV mở bài tập tương tác: HS đặt tính và tính ra vở trước rồi nhập kết quả; khi máy báo sai</t>
         </is>
       </c>
     </row>
@@ -19060,7 +19202,12 @@
           <t>106</t>
         </is>
       </c>
-      <c r="H109" s="4" t="inlineStr"/>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Hình thành kiến thức bài “Chia cho số có hai chữ số”, GV chiếu tranh những chiếc thuyền và hành khách rồi hiện dần phép chia đặt tính
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở hoạt động Luyện tập, GV mở bài tập tương tác: HS tính ra vở trước rồi nhập kết quả; khi máy báo sai</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="inlineStr">
@@ -19828,7 +19975,8 @@
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Khám phá bài “Rút gọn phân số”, GV chiếu hình băng giấy chia phần lên màn hình.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Khám phá bài “Rút gọn phân số”, GV chiếu hình băng giấy chia phần lên màn hình rồi gộp dần các phần bằng nhau
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở hoạt động Luyện tập, GV mở bài tập tương tác: HS rút gọn ra vở trước rồi nhập kết quả; khi máy báo sai</t>
         </is>
       </c>
     </row>
@@ -19886,7 +20034,12 @@
           <t>132</t>
         </is>
       </c>
-      <c r="H135" s="4" t="inlineStr"/>
+      <c r="H135" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Khám phá bài “Quy đồng mẫu số các phân số”, GV chiếu hai băng giấy chia phần khác nhau lên màn hình rồi chia nhỏ dần cho tới khi hai băng…
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở hoạt động Luyện tập, GV mở bài tập tương tác: HS quy đồng ra vở trước rồi nhập kết quả; khi máy báo sai</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="inlineStr">
@@ -20141,7 +20294,8 @@
       </c>
       <c r="H143" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Khám phá bài “Phép cộng phân số”, GV chiếu băng giấy đã tô màu một phần tám.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Khám phá bài “Phép cộng phân số”, GV chiếu băng giấy đã tô màu một phần tám và một phần hai lên màn hình rồi chia nhỏ dần cho tới khi…
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở hoạt động Luyện tập, GV mở bài tập tương tác: HS cộng ra vở trước rồi nhập kết quả; khi máy báo sai</t>
         </is>
       </c>
     </row>
@@ -20251,7 +20405,12 @@
           <t>144</t>
         </is>
       </c>
-      <c r="H147" s="4" t="inlineStr"/>
+      <c r="H147" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Khám phá bài “Phép trừ phân số”, GV chiếu hình chiếc bánh chia tám phần lên màn hình
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở hoạt động Luyện tập, GV mở bài tập tương tác: HS trừ ra vở trước rồi nhập kết quả; khi máy báo sai</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="4" t="inlineStr">
@@ -20431,7 +20590,12 @@
           <t>150</t>
         </is>
       </c>
-      <c r="H153" s="4" t="inlineStr"/>
+      <c r="H153" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Khám phá bài “Phép nhân phân số”, GV chiếu hình chữ nhật chia ô lên màn hình rồi tô màu lần lượt theo chiều dài và chiều rộng
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở hoạt động Luyện tập, GV mở bài tập tương tác: HS nhân ra vở trước rồi nhập kết quả; khi máy báo sai, các em xem lại đã nhân đúng tử với tử</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="4" t="inlineStr">
@@ -20545,7 +20709,8 @@
       </c>
       <c r="H157" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Khám phá bài “Phép chia phân số”, GV chiếu hình băng giấy chia phần lên màn hình.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Khám phá bài “Phép chia phân số”, GV chiếu hình băng giấy chia phần lên màn hình rồi cho thấy chia cho một phân số chính là nhân với phân số…
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở hoạt động Luyện tập, GV mở bài tập tương tác: HS chia ra vở trước rồi nhập kết quả; khi máy báo sai</t>
         </is>
       </c>
     </row>
@@ -21587,7 +21752,8 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở bài “Yêu lao động”, GV chiếu bộ ảnh người lao động ở nhiều nghề.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài “Yêu lao động”, GV chiếu bộ ảnh người lao động ở nhiều nghề và ảnh HS làm việc vừa sức như trực nhật, tưới cây, gấp quần áo
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV gõ lên màn hình những việc HS kể thành bảng hai cột việc ở nhà và việc ở trường; cả lớp cùng đọc
 KNS: KN chi tiêu và giữ gìn: dùng đồ dùng, tiền bạc hợp lí, giữ gìn của công.</t>
         </is>
       </c>
@@ -22671,7 +22837,8 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Sau khi các nhóm làm thí nghiệm với túi ni lông và chậu nước, HS ghi kết quả vào bảng chiếu trên màn hình.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Mở đầu bài “Không khí có ở đâu?”, GV chiếu đoạn phim hoạt hình về không khí xung quanh ta, dừng hình ở cảnh bong bóng khí nổi lên trong nước
+Năng lực số Miền 5 (Cơ bản, bậc 2): Sau khi các nhóm làm thí nghiệm với túi ni lông và chậu nước, HS ghi kết quả vào bảng chiếu trên màn hình; khi nhóm nào ra kết quả khác</t>
         </is>
       </c>
     </row>
@@ -23209,7 +23376,8 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở bài “Nhiệt độ và sự truyền nhiệt”, GV chiếu ảnh phóng to mặt nhiệt kế.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài “Nhiệt độ và sự truyền nhiệt”, GV chiếu ảnh phóng to mặt nhiệt kế để cả lớp cùng đọc đúng số chỉ
+Năng lực số Miền 5 (Cơ bản, bậc 2): HS ghi kết quả đo vào bảng chiếu trên màn hình rồi cùng đối chiếu; khi số liệu các nhóm khác nhau, cả lớp tìm nguyên nhân là đặt nhiệt kế gần cửa sổ</t>
         </is>
       </c>
     </row>
@@ -23273,7 +23441,8 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): HS ghi kết quả thí nghiệm vào bảng chiếu trên màn hình.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài vật dẫn nhiệt tốt và vật dẫn nhiệt kém, GV chiếu mô phỏng nhiệt truyền qua thìa kim loại và thìa gỗ cắm trong cốc nước nóng
+Năng lực số Miền 5 (Cơ bản, bậc 2): HS ghi kết quả thí nghiệm vào bảng chiếu trên màn hình rồi đối chiếu với dự đoán; khi kết quả các nhóm khác nhau</t>
         </is>
       </c>
     </row>
@@ -25409,6 +25578,8 @@
       <c r="H24" s="4" t="inlineStr">
         <is>
           <t>Bổ sung bài còn thiếu theo mục lục SGK (Tổ CM đối chiếu SGK)
+Năng lực số Miền 1 (Cơ bản, bậc 2): HS tra số liệu dân số, mật độ dân cư của vùng trong bài “Dân cư và hoạt động sản xuất ở vùng đồng bằng Bắc Bộ” từ nguồn chính thống
+Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu phim ngắn về hoạt động sản xuất tiêu biểu của vùng (trồng chè, khai thác khoáng sản, đánh bắt và nuôi trồng thuỷ sản, làm muối)
 QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
         </is>
       </c>
@@ -25499,7 +25670,8 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS mô tả được nét đặc sắc của lễ hội, nét văn hoá vùng miền nhờ phim tư liệu chính thống.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu phim tư liệu về “Một số nét văn hóa ở vùng đồng bằng Bắc Bộ” do đài truyền hình, cơ quan văn hoá công bố: phần lễ, phần hội, trang phục
+Năng lực số Miền 3 (Cơ bản, bậc 2): HS làm một sản phẩm số nhỏ giới thiệu lễ hội hoặc nét văn hoá vừa học: trang chiếu có ảnh và chú thích, hoặc đoạn thuyết minh ghi âm
 QPAN: Liên hệ vai trò của mỗi vùng đối với quốc phòng, an ninh; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
         </is>
       </c>
@@ -26209,7 +26381,12 @@
           <t>47</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr"/>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Tìm hiểu vùng đất hội tụ nhiều di sản của bài “Một số nét văn hoá ở vùng Bắc Trung Bộ và Nam Trung Bộ”
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động nhóm, GV chiếu bảng chung “Di sản – Nơi có – Nét đặc sắc”; các nhóm lên điền rồi đọc bảng của nhau</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -26267,8 +26444,9 @@
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>QPAN: Giáo dục truyền thống dựng nước và giữ nước, tinh thần chống giặc ngoại xâm của dân tộc; bồi dưỡng niềm tự hào dân tộc và lòng biết ơn các anh hùng, liệt sĩ đã hi sinh bảo vệ Tổ quốc.
-KNS: KN ứng phó với thiên tai thường gặp ở địa phương.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Mở đầu bài “Truyền thống yêu nước, cách mạng của đồng bào Bắc Trung Bộ và Nam Trung Bộ”, GV chiếu trò chơi lật mảnh ghép trên màn hình
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động nhóm, GV chiếu bảng chung “Di tích, nhân vật – Nơi có – Điều đáng nhớ”; các nhóm lên điền rồi đọc bảng của nhau
+QPAN: Giáo dục truyền thống dựng nước và giữ nước, tinh thần chống giặc ngoại xâm của dân tộc; bồi dưỡng niềm tự hào dân tộc và lòng biết ơn các anh hùng, liệt sĩ đã hi sinh bảo vệ Tổ quốc.</t>
         </is>
       </c>
     </row>
@@ -27091,7 +27269,12 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 2 (Cơ bản, bậc 2): Mở đầu bài “Hello again”, GV chỉ vào máy chiếu và hỏi What should we do when we use the big screen?
+Năng lực số Miền 1 (Cơ bản, bậc 2): GV bật bản ghi âm bản ngữ đoạn Ms Hoa chào và giới thiệu các bạn trong lớp, cho nghe hai lần; HS nghe và tích đúng tranh trên màn hình</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -27121,7 +27304,12 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Trong bài “Classroom activities”, GV bật ghi âm bản ngữ bốn câu tả các bạn đang làm gì trong lớp giờ ra chơi như reading a book, drawing a picture, playing chess; HS nghe
+Năng lực số Miền 3 (Cơ bản, bậc 2): Sau khi tập chant, GV dùng điện thoại quay nhóm HS diễn chant kèm động tác read a book, draw a picture rồi chiếu ngay lên tivi; lớp nhận xét nhóm nào đọc rõ</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -27151,7 +27339,12 @@
           <t>4</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu flashcard số các hoạt động ngoài trời trong bài “Outdoor activities”: skipping, playing football, playing badminton, flying a kite, riding a bike; HS nhìn tranh
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV tổ chức trò chơi nghe–chọn tranh trên màn hình: bật ghi âm I like flying a kite. / She likes skipping., HS chọn tranh đúng</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -27252,7 +27445,9 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 2 (Cơ bản, bậc 2): Trong bài “My friends — Lesson 2 (1-3)”, GV chiếu tranh các cách làm quen với bạn ở xa: gặp trực tiếp, gọi video có người lớn bên cạnh
+Năng lực số Miền 1 (Cơ bản, bậc 2): GV bật ghi âm bản ngữ hai tình huống hỏi đáp Where’s he / she from?, dừng sau từng câu để HS nhắc lại; GV chiếu flashcard số các bạn Tony, Linda
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -27320,7 +27515,8 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở bài Unit 1 My friends, GV mở tệp ghi âm phần hội thoại hỏi bạn đến từ đâu, chiếu tranh kèm.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài Unit 1 My friends, GV mở tệp ghi âm phần hội thoại hỏi bạn đến từ đâu, chiếu tranh kèm lời thoại lên màn hình
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt hỏi đáp theo cặp của HS rồi mở lại; các em nghe và tự đánh giá theo hai tiêu chí chiếu trên màn hình là nói đủ câu và phát…
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -27390,7 +27586,9 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 2 Time and daily routines, GV chiếu mặt đồng hồ số cùng tranh sinh hoạt trong ngày và mở tệp ghi âm mẫu câu hỏi giờ, trả lời giờ
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu bảng thời gian biểu trống của lớp lên màn hình; từng cặp HS hỏi đáp giờ bạn thức dậy, đi học, ăn tối rồi đọc để GV điền vào bảng
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -27424,7 +27622,9 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài Unit 2 Time and daily routines, GV chiếu bộ tranh việc làm trong ngày kèm mặt đồng hồ và mở tệp ghi âm mẫu
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe và chọn tranh đúng, kéo kim đồng hồ về giờ vừa nghe; máy chấm ngay nên HS nhận ra mình còn nhầm giờ hơn với giờ kém
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -27458,7 +27658,8 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Mở bài tập tương tác nghe và chọn tranh đúng, kéo kim đồng hồ về giờ vừa nghe.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài Unit 2 Time and daily routines, GV chiếu bộ tranh việc làm trong ngày kèm mặt đồng hồ và mở tệp ghi âm mẫu
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe và chọn tranh đúng, kéo kim đồng hồ về giờ vừa nghe; máy chấm ngay nên HS nhận ra mình còn nhầm giờ hơn với giờ kém
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -27527,7 +27728,9 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần luyện nói của bài Unit 2 Time and daily routines, GV chiếu bảng thời gian biểu trống của lớp; từng cặp HS hỏi đáp giờ bạn thức dậy, đi học
+Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi nhóm làm một thời gian biểu bằng hình: chọn biểu tượng việc làm, ghi giờ bên cạnh và viết hai câu tiếng Anh giới thiệu
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -27561,7 +27764,9 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 2 Time and daily routines, GV chiếu mặt đồng hồ số cùng tranh sinh hoạt trong ngày và mở tệp ghi âm mẫu câu hỏi giờ, trả lời giờ
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu bảng thời gian biểu trống của lớp lên màn hình; từng cặp HS hỏi đáp giờ bạn thức dậy, đi học, ăn tối rồi đọc để GV điền vào bảng
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -27595,7 +27800,8 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Vào bài Unit 3 My week, GV chiếu bộ thẻ các thứ trong tuần.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 3 My week, GV chiếu bộ thẻ các thứ trong tuần kèm tệp ghi âm; HS nghe rồi sắp các thứ theo đúng thứ tự trên màn hình
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe chọn tranh và điền thứ còn thiếu vào câu; máy chấm ngay nên HS nhận ra mình còn nhầm hai thứ có cách đọc gần giống nhau
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -27630,7 +27836,9 @@
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần luyện âm của bài Unit 3 My week, GV mở tệp ghi âm từ và câu chứa âm u, phát chậm rồi phát bình thường; HS nghe
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe rồi chọn từ có chứa âm vừa học và nối câu với tranh; máy chấm ngay nên HS nhận ra mình còn nhầm từ nào
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -27664,7 +27872,9 @@
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 2 (Cơ bản, bậc 2): Ở bài Unit 3 My week phần luyện nói, GV chiếu thời khoá biểu trống của lớp trên màn hình; từng cặp HS hỏi đáp bằng tiếng Anh xem thứ mấy có môn gì
+Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi nhóm làm một trang giới thiệu tuần học của mình: chọn biểu tượng môn học, ghi thứ bên cạnh và viết hai câu tiếng Anh
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -27732,7 +27942,8 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Mở bài tập tương tác nghe.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần luyện âm của bài Unit 3 My week, GV mở tệp ghi âm từ và câu chứa âm u, phát chậm rồi phát bình thường; HS nghe
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe rồi chọn từ có chứa âm vừa học và nối câu với tranh; máy chấm ngay nên HS nhận ra mình còn nhầm từ nào
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -27767,7 +27978,9 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 3 My week, GV chiếu bộ thẻ các thứ trong tuần kèm tệp ghi âm; HS nghe rồi sắp các thứ theo đúng thứ tự trên màn hình
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe chọn tranh và điền thứ còn thiếu vào câu; máy chấm ngay nên HS nhận ra mình còn nhầm hai thứ có cách đọc gần giống nhau
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -27801,7 +28014,9 @@
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 4 My birthday party, GV chiếu tranh bữa tiệc sinh nhật kèm tệp ghi âm mẫu; HS nghe rồi chỉ đúng đồ vật, hoạt động trong tranh
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu bảng khảo sát ngày sinh nhật của lớp theo tháng; từng cặp HS hỏi đáp bằng tiếng Anh rồi đọc để thầy cô điền vào bảng
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -27904,7 +28119,9 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài Unit 4 My birthday party, GV chiếu bộ tranh đồ vật và hoạt động trong bữa tiệc kèm tệp ghi âm; HS nghe rồi nối từ với tranh
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe chọn tranh đúng và điền từ còn thiếu vào lời mời; máy chấm ngay nên HS nhận ra mình còn nhầm hai từ gần giống nhau
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -27938,7 +28155,9 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần luyện âm và nghe của bài Unit 4 My birthday party, GV mở tệp ghi âm phát chậm rồi phát bình thường; HS nghe
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt hỏi đáp về bữa tiệc sinh nhật của vài cặp rồi mở cho cả lớp nghe; HS nhận xét theo tiêu chí nói đủ câu, phát âm rõ
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -28006,7 +28225,8 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 2): Chiếu bảng ba cột tên bạn, việc bạn làm được.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 5 Things we can do, GV chiếu bộ tranh hoạt động kèm tệp ghi âm mẫu; HS nghe rồi nối việc làm với tranh
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu bảng ba cột tên bạn, việc bạn làm được và việc bạn muốn học; từng cặp hỏi đáp bằng tiếng Anh rồi đọc để thầy cô điền
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -28041,7 +28261,9 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần kĩ năng của bài Unit 5 Things we can do, GV mở bài hát và học liệu của bài trên kho học liệu số của ngành rồi chỉ cho HS thấy đường…
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe chọn tranh và điền từ còn thiếu vào câu; máy chấm ngay nên HS nhận ra mình còn nhầm chỗ nào, nghe lại đoạn đó
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -28075,7 +28297,9 @@
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần luyện tập bài Unit 5 Things we can do, GV mở bài tập tương tác nghe chọn tranh và điền từ còn thiếu vào câu nói về khả năng
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt hỏi đáp của vài cặp rồi mở cho cả lớp nghe; HS nhận xét theo tiêu chí nói đủ câu, phát âm rõ, dùng đúng mẫu câu
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -28143,7 +28367,8 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở phần kĩ năng của bài Unit 5 Things we can do.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần kĩ năng của bài Unit 5 Things we can do, GV mở bài hát và học liệu của bài trên kho học liệu số của ngành rồi chỉ cho HS thấy đường…
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe chọn tranh và điền từ còn thiếu vào câu; máy chấm ngay nên HS nhận ra mình còn nhầm chỗ nào, nghe lại đoạn đó
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -28178,7 +28403,9 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 5 Things we can do, GV chiếu bộ tranh hoạt động kèm tệp ghi âm mẫu; HS nghe rồi nối việc làm với tranh
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu bảng ba cột tên bạn, việc bạn làm được và việc bạn muốn học; từng cặp hỏi đáp bằng tiếng Anh rồi đọc để thầy cô điền
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -28240,7 +28467,12 @@
           <t>36</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr"/>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở tiết Review 1 phần nghe và đọc, GV mở bộ bài tập tương tác tổng hợp các chủ điểm đã học; sau mỗi câu máy báo đúng
+Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu bảng tổng hợp từ vựng và mẫu câu của các bài đã học, bấm sáng dần từng nhóm; HS nhìn bảng để nhớ lại theo chủ điểm chứ không học rời rạc</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -28272,7 +28504,8 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Ở tiết hoạt động mở rộng, GV mở bộ bài tập tương tác tổng hợp các chủ điểm đã học.</t>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở tiết hoạt động mở rộng, GV mở bộ bài tập tương tác tổng hợp các chủ điểm đã học; sau mỗi câu máy báo đúng
+Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi nhóm làm một trò chơi ôn tập nhỏ trên giấy hoặc trên máy: viết năm câu hỏi kèm đáp án theo chủ điểm đã học</t>
         </is>
       </c>
     </row>
@@ -28306,7 +28539,9 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 6 Our school facilities, GV chiếu ảnh các phòng chức năng của trường kèm tệp ghi âm mẫu; HS nghe rồi nối tên phòng với ảnh
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu bảng liệt kê phòng chức năng của trường; từng cặp HS hỏi đáp bằng tiếng Anh xem trường mình có phòng nào rồi đọc để thầy cô đánh dấu
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -28374,7 +28609,9 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở bài Unit 6 phần luyện tập, GV mở bài tập tương tác nghe chọn tranh và ghép câu hỏi với câu trả lời về phòng chức năng
+Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi nhóm làm một trang giới thiệu trường mình bằng tiếng Anh: chọn ba ảnh phòng chức năng, ghi tên và viết một câu về hoạt động ở đó
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -28990,7 +29227,8 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Look, listen and repeat của Unit 9 “Our sports day”.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 9 “Our sports day”, GV chiếu tranh các môn thi đấu trong ngày hội thể thao lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Unscramble the letters, GV chiếu các chữ cái bị đảo của tên tháng lên màn hình; các nhóm bàn nhau sắp lại thành từ đúng rồi lên bấm chọn
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -29059,7 +29297,9 @@
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 9 “Our sports day”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động Let's chant, GV mở bản chant có chữ chạy theo nhịp trên màn hình để cả lớp đọc đồng thanh đúng tiết tấu
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -29093,7 +29333,9 @@
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 9 “Our sports day”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động Let's chant, GV mở bản chant có chữ chạy theo nhịp trên màn hình để cả lớp đọc đồng thanh đúng tiết tấu
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -29127,7 +29369,8 @@
       </c>
       <c r="H65" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 2): Ở hoạt động Point and say, GV chiếu bảng chung “Nơi đã đến – Việc đã làm”.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 10 “Our summer holidays”, GV chiếu tranh các kì nghỉ hè lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động Point and say, GV chiếu bảng chung “Nơi đã đến – Việc đã làm”; các cặp hỏi đáp rồi lên điền câu trả lời của bạn mình vào bảng
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -29162,7 +29405,9 @@
       </c>
       <c r="H66" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 10 “Our summer holidays”, GV mở bản nghe mẫu âm ere trong từ were
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Board race, GV chiếu chủ đề lên màn hình, hai đội thay nhau viết từ đã học
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -29196,7 +29441,9 @@
       </c>
       <c r="H67" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and number của Unit 10 “Our summer holidays”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh số
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát Were you on the beach yesterday? có lời chạy trên màn hình để cả lớp hát đồng thanh
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -29264,7 +29511,8 @@
       </c>
       <c r="H69" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Listen and repeat của Unit 10 “Our summer holidays”, GV mở bản nghe mẫu âm ere trong từ were, cho nghe chậm.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 10 “Our summer holidays”, GV mở bản nghe mẫu âm ere trong từ were
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Board race, GV chiếu chủ đề lên màn hình, hai đội thay nhau viết từ đã học
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -29299,7 +29547,9 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 10 “Our summer holidays”, GV chiếu tranh các kì nghỉ hè lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động Point and say, GV chiếu bảng chung “Nơi đã đến – Việc đã làm”; các cặp hỏi đáp rồi lên điền câu trả lời của bạn mình vào bảng
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -29363,7 +29613,8 @@
       </c>
       <c r="H72" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 2): Ở phần Practice, GV chiếu bảng chung các mẫu câu của Unit 6 đến Unit 10.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Read and match của Review 2, GV chiếu các cặp câu và tranh lên màn hình, cho hiện lần lượt từng cặp để HS đọc, nối thử rồi mở đáp án
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Practice, GV chiếu bảng chung các mẫu câu của Unit 6 đến Unit 10; mỗi nhóm lên đặt một câu theo mẫu và ghi vào bảng</t>
         </is>
       </c>
     </row>
@@ -29395,7 +29646,12 @@
           <t>70</t>
         </is>
       </c>
-      <c r="H73" s="4" t="inlineStr"/>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Read and match của Extension activities 2, GV chiếu hai đoạn đọc về vùng quê và thành phố cùng bộ tranh lên màn hình; HS đọc thầm
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần luyện tập, GV mở bài tập tương tác điền từ vào chỗ trống của hai đoạn đọc; HS chọn từ rồi bấm kiểm tra</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
@@ -29487,7 +29743,8 @@
       </c>
       <c r="H76" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Look, listen and repeat của Unit 11 “My home”, GV chiếu tranh các phòng trong nhà lên màn hình.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 11 “My home”, GV chiếu tranh các phòng trong nhà lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bản chant về ngôi nhà có chữ chạy theo nhịp; sau khi nghe, các nhóm sắp lại các thẻ từ chỉ phòng theo đúng thứ tự xuất hiện trong…</t>
         </is>
       </c>
     </row>
@@ -29521,7 +29778,9 @@
       </c>
       <c r="H77" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 11 “My home”, GV mở bản nghe mẫu âm của các chữ cái trong bài
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát My house có lời chạy trên màn hình cho cả lớp hát; sau đó chia hai nhóm hát nối tiếp theo phần lời đang sáng và nghe…
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -29589,7 +29848,9 @@
       </c>
       <c r="H79" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Vocabulary của Unit 11 “My home”, GV chiếu tranh đồ vật trong nhà kèm từ và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Whispering, sau mỗi lượt truyền tin GV chiếu câu gốc lên màn hình; hai đội đối chiếu câu mình nói với câu gốc
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -29623,7 +29884,8 @@
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 2): Ở phần Warm-up, GV mở bài hát My house có lời chạy trên màn hình cho cả lớp hát.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Vocabulary của Unit 11 “My home”, GV chiếu tranh đồ vật trong nhà kèm từ và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Whispering, sau mỗi lượt truyền tin GV chiếu câu gốc lên màn hình; hai đội đối chiếu câu mình nói với câu gốc
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -29658,7 +29920,9 @@
       </c>
       <c r="H81" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 11 “My home”, GV mở bản nghe mẫu âm của các chữ cái trong bài
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát My house có lời chạy trên màn hình cho cả lớp hát; sau đó chia hai nhóm hát nối tiếp theo phần lời đang sáng và nghe…
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -29692,7 +29956,9 @@
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 11 “My home”, GV chiếu tranh các phòng trong nhà lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bản chant về ngôi nhà có chữ chạy theo nhịp; sau khi nghe, các nhóm sắp lại các thẻ từ chỉ phòng theo đúng thứ tự xuất hiện trong…
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -29726,7 +29992,9 @@
       </c>
       <c r="H83" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 12 “Jobs”, GV chiếu tranh những người đang làm việc kèm tên nghề lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Guess the job, GV chiếu lần lượt ảnh một đồ vật gắn với nghề như ống nghe, thước thợ, bảng phấn
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -29760,7 +30028,8 @@
       </c>
       <c r="H84" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Vocabulary của Unit 12 “Jobs”, GV chiếu tranh nơi làm việc.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Vocabulary của Unit 12 “Jobs”, GV chiếu tranh nơi làm việc kèm từ mới lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần luyện nói, GV chiếu bảng chung “Nghề – Nơi làm việc – Câu nói bằng tiếng Anh”; các cặp hỏi đáp rồi lên điền câu của mình
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -29795,7 +30064,9 @@
       </c>
       <c r="H85" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 12 “Jobs”, GV mở bản nghe mẫu các từ chỉ nghề, cho nghe chậm rồi nghe lại tốc độ thường và chiếu chữ có đánh dấu…
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Lip-reading, GV chiếu từ chỉ nghề riêng cho bạn nhìn, bạn nói không thành tiếng để nhóm đoán
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -29863,7 +30134,9 @@
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 12 “Jobs”, GV chiếu tranh những người đang làm việc kèm tên nghề lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Guess the job, GV chiếu lần lượt ảnh một đồ vật gắn với nghề như ống nghe, thước thợ, bảng phấn
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -29897,7 +30170,8 @@
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Nhân vật – Đặc điểm ngoại hình”.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 12 “Jobs”, GV mở bản nghe mẫu các từ chỉ nghề, cho nghe chậm rồi nghe lại tốc độ thường và chiếu chữ có đánh dấu…
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Lip-reading, GV chiếu từ chỉ nghề riêng cho bạn nhìn, bạn nói không thành tiếng để nhóm đoán
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -29932,7 +30206,9 @@
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 13 “Appearance”, GV chiếu tranh các nhân vật với ngoại hình khác nhau và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Nhân vật – Đặc điểm ngoại hình”; các cặp hỏi đáp về nhân vật trong tranh rồi lên điền câu của mình
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -29966,7 +30242,9 @@
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 13 “Appearance”, GV mở bản nghe mẫu các câu mô tả ngoại hình
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi truyền tin, sau mỗi lượt GV chiếu câu gốc mô tả một người lên màn hình; hai đội đối chiếu câu mình nói với câu gốc
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -30000,7 +30278,9 @@
       </c>
       <c r="H91" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 13 “Appearance”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu người được tả
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát What do your parents look like? có lời chạy trên màn hình cho cả lớp hát
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -30034,7 +30314,8 @@
       </c>
       <c r="H92" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Listen and repeat của Unit 13 “Appearance”, GV mở bản nghe mẫu các câu mô tả ngoại hình, cho nghe chậm.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 13 “Appearance”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu người được tả
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát What do your parents look like? có lời chạy trên màn hình cho cả lớp hát
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -30069,7 +30350,9 @@
       </c>
       <c r="H93" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 13 “Appearance”, GV mở bản nghe mẫu các câu mô tả ngoại hình
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi truyền tin, sau mỗi lượt GV chiếu câu gốc mô tả một người lên màn hình; hai đội đối chiếu câu mình nói với câu gốc
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -30103,7 +30386,9 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 13 “Appearance”, GV chiếu tranh các nhân vật với ngoại hình khác nhau và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Nhân vật – Đặc điểm ngoại hình”; các cặp hỏi đáp về nhân vật trong tranh rồi lên điền câu của mình
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -30137,7 +30422,9 @@
       </c>
       <c r="H95" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Vocabulary của Unit 14 “Daily activities”, GV chiếu tranh các việc làm hằng ngày kèm từ mới lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Giờ – Việc em làm”; các cặp hỏi đáp về thời gian biểu của nhau rồi lên điền câu của mình
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -30171,7 +30458,8 @@
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 2): Ở phần Warm-up trò chơi Change chairs, GV chiếu câu lệnh lên màn hình.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 14 “Daily activities”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Spelling Bee, GV chiếu từ đã học lên màn hình rồi che đi, các nhóm đánh vần lại
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -30206,7 +30494,9 @@
       </c>
       <c r="H97" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Vocabulary của Unit 14 “Daily activities”, GV chiếu tranh các việc làm trong ngày kèm từ mới lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Change chairs, GV chiếu câu lệnh lên màn hình để cả lớp cùng đọc; HS nghe và đổi chỗ nếu câu đúng với mình
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30564,9 @@
       </c>
       <c r="H99" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Vocabulary của Unit 14 “Daily activities”, GV chiếu tranh các việc làm hằng ngày kèm từ mới lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Giờ – Việc em làm”; các cặp hỏi đáp về thời gian biểu của nhau rồi lên điền câu của mình
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -30308,7 +30600,8 @@
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Look, listen and repeat của Unit 15 “My family's weekends”.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 14 “Daily activities”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Spelling Bee, GV chiếu từ đã học lên màn hình rồi che đi, các nhóm đánh vần lại
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -30343,7 +30636,9 @@
       </c>
       <c r="H101" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 15 “My family's weekends”, GV chiếu tranh các địa điểm trong thị trấn kèm tên gọi lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Nơi đến cuối tuần – Việc làm ở đó”; các cặp hỏi đáp rồi lên điền câu của mình
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -30377,7 +30672,9 @@
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 15 “My family's weekends”, GV mở bản nghe mẫu, cho nghe chậm rồi nghe lại tốc độ thường và chiếu câu có đánh dấu trọng âm…
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Matching, GV chiếu hai cột từ và tranh bị xáo trộn; các nhóm nối thử rồi bấm kiểm tra
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -30480,7 +30777,9 @@
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 15 “My family's weekends”, GV mở bản nghe mẫu, cho nghe chậm rồi nghe lại tốc độ thường và chiếu câu có đánh dấu trọng âm…
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Matching, GV chiếu hai cột từ và tranh bị xáo trộn; các nhóm nối thử rồi bấm kiểm tra
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -30514,7 +30813,9 @@
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 15 “My family's weekends”, GV chiếu tranh các địa điểm trong thị trấn kèm tên gọi lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Nơi đến cuối tuần – Việc làm ở đó”; các cặp hỏi đáp rồi lên điền câu của mình
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -30608,7 +30909,8 @@
       </c>
       <c r="H109" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Vocabulary của Unit 16 “Weather”, GV chiếu tranh các kiểu thời tiết.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Vocabulary của Unit 16 “Weather”, GV chiếu tranh các kiểu thời tiết kèm từ mới lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Nơi – Thời tiết hôm nay – Câu nói bằng tiếng Anh”; các cặp hỏi đáp rồi lên điền</t>
         </is>
       </c>
     </row>
@@ -30676,7 +30978,9 @@
       </c>
       <c r="H111" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 16 “Weather”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu kiểu thời tiết
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát What was the weather like? có lời chạy trên màn hình cho cả lớp hát
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -30744,7 +31048,8 @@
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Ở phần Warm-up trò chơi Slap the board, GV chiếu các từ đã học lên màn hình.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 16 “Weather”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu kiểu thời tiết
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát What was the weather like? có lời chạy trên màn hình cho cả lớp hát
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -30779,7 +31084,9 @@
       </c>
       <c r="H114" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 16 “Weather”, GV mở bản nghe mẫu hai âm được học, cho nghe chậm rồi nghe lại tốc độ thường và chiếu câu ví dụ có…
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Slap the board, GV chiếu các từ đã học lên màn hình; hai đội nghe GV đọc rồi lên chạm đúng từ
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -30813,7 +31120,9 @@
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Vocabulary của Unit 16 “Weather”, GV chiếu tranh các kiểu thời tiết kèm từ mới lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Nơi – Thời tiết hôm nay – Câu nói bằng tiếng Anh”; các cặp hỏi đáp rồi lên điền
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -30847,7 +31156,9 @@
       </c>
       <c r="H116" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 17 “In the city”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu nơi được nhắc tới
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Memory game, GV chiếu bộ thẻ từ chỉ đường và địa điểm rồi giấu dần từng thẻ; các nhóm nhớ và gọi tên thẻ đã mất
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -30881,7 +31192,8 @@
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Look, listen and repeat của Unit 17 “In the city”, GV chiếu sơ đồ đường phố lên màn hình.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 17 “In the city”, GV chiếu tranh các địa điểm trong thành phố kèm tên gọi lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Địa điểm – Việc làm ở đó”; các cặp hỏi đáp rồi lên điền câu của mình
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -30916,7 +31228,9 @@
       </c>
       <c r="H118" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 17 “In the city”, GV chiếu sơ đồ đường phố lên màn hình và mở bản nghe mẫu các câu chỉ đường
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bản đồ khu phố có đánh dấu điểm xuất phát và đích đến; các cặp thay nhau chỉ đường bằng tiếng Anh
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -30984,7 +31298,9 @@
       </c>
       <c r="H120" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 17 “In the city”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu nơi được nhắc tới
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Memory game, GV chiếu bộ thẻ từ chỉ đường và địa điểm rồi giấu dần từng thẻ; các nhóm nhớ và gọi tên thẻ đã mất
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -31018,7 +31334,8 @@
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>NLS-GT (Cơ bản 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Gian hàng – Thứ mua được ở đó”.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 17 “In the city”, GV chiếu tranh các địa điểm trong thành phố kèm tên gọi lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Địa điểm – Việc làm ở đó”; các cặp hỏi đáp rồi lên điền câu của mình
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -31053,7 +31370,9 @@
       </c>
       <c r="H122" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 18 “At the shopping centre”, GV chiếu tranh trung tâm mua sắm kèm tên các gian hàng và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Gian hàng – Thứ mua được ở đó”; các cặp hỏi đáp rồi lên điền câu của mình
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -31087,7 +31406,9 @@
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 18 “At the shopping centre”, GV mở bản nghe mẫu, cho nghe chậm rồi nghe lại tốc độ thường và chiếu câu có đánh dấu chỗ…
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Guess the price, GV chiếu ảnh món hàng cùng vài mức giá; các nhóm đoán giá bằng tiếng Anh rồi bấm chọn
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -31155,7 +31476,8 @@
       </c>
       <c r="H125" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Listen and repeat của Unit 18 “At the shopping centre”, GV mở bản nghe mẫu, cho nghe chậm.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 18 “At the shopping centre”, GV mở bản nghe mẫu, cho nghe chậm rồi nghe lại tốc độ thường và chiếu câu có đánh dấu chỗ…
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Guess the price, GV chiếu ảnh món hàng cùng vài mức giá; các nhóm đoán giá bằng tiếng Anh rồi bấm chọn
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -31190,7 +31512,9 @@
       </c>
       <c r="H126" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 18 “At the shopping centre”, GV chiếu tranh trung tâm mua sắm kèm tên các gian hàng và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Gian hàng – Thứ mua được ở đó”; các cặp hỏi đáp rồi lên điền câu của mình
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -31258,7 +31582,9 @@
       </c>
       <c r="H128" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 19, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu con vật được nhắc tới
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Con vật – Nơi sống – Thức ăn”; các cặp hỏi đáp rồi lên điền câu của mình
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -31292,7 +31618,8 @@
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Ở phần Warm-up trò chơi đoán con vật, GV chiếu ảnh bị che phần lớn.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 19 “The animal world”, GV chiếu tranh các loài vật kèm tên gọi lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Con vật – Nơi sống – Đặc điểm”; các cặp hỏi đáp rồi lên điền câu của mình
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -31327,7 +31654,9 @@
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 19 “The animal world”, GV chiếu tranh loài vật lên màn hình và mở bản nghe mẫu các câu mô tả
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi đoán con vật, GV chiếu ảnh bị che phần lớn; các nhóm đoán tên bằng tiếng Anh rồi giơ tay trả lời
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -31395,7 +31724,9 @@
       </c>
       <c r="H132" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 19, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu con vật được nhắc tới
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Con vật – Nơi sống – Thức ăn”; các cặp hỏi đáp rồi lên điền câu của mình
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -31429,7 +31760,8 @@
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Look, listen and repeat của Unit 20 “At summer camp”, GV chiếu tranh các hoạt động ở trại hè.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 19 “The animal world”, GV chiếu tranh các loài vật kèm tên gọi lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Con vật – Nơi sống – Đặc điểm”; các cặp hỏi đáp rồi lên điền câu của mình
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -31464,7 +31796,9 @@
       </c>
       <c r="H134" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 20 “At summer camp”, GV chiếu tranh các hoạt động ở trại hè kèm tên gọi và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Hoạt động ở trại hè – Vì sao em thích”; các cặp hỏi đáp rồi lên điền câu của mình
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -31566,7 +31900,8 @@
       </c>
       <c r="H137" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Ở phần Warm-up trò chơi Lip-reading, GV chiếu từ riêng cho bạn nhìn, bạn nói không thành tiếng.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 20 “At summer camp”, GV mở bản nghe mẫu, cho nghe chậm rồi nghe lại tốc độ thường và chiếu câu có đánh dấu chỗ nhấn…
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Lip-reading, GV chiếu từ riêng cho bạn nhìn, bạn nói không thành tiếng để nhóm đoán
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -31601,7 +31936,9 @@
       </c>
       <c r="H138" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 20 “At summer camp”, GV chiếu tranh các hoạt động ở trại hè kèm tên gọi và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Hoạt động ở trại hè – Vì sao em thích”; các cặp hỏi đáp rồi lên điền câu của mình
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -31669,7 +32006,8 @@
       </c>
       <c r="H140" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở phần Fun time của Review 4, GV chiếu lần lượt các nhóm từ đã học lên màn hình cho HS đọc.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Fun time của Review 4, GV chiếu lần lượt các nhóm từ đã học lên màn hình cho HS đọc và tìm từ khác loại
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần luyện tập, GV mở bài tập tương tác nối câu hỏi với câu trả lời của các đơn vị đã học; HS chọn rồi bấm kiểm tra</t>
         </is>
       </c>
     </row>
@@ -31937,7 +32275,8 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>NLS-ST (Cơ bản 2): Ở bài “Gõ bàn phím đúng cách”.</t>
+          <t>Năng lực số Miền 3 (Cơ bản, bậc 2): Ở bài “Gõ bàn phím đúng cách”, GV hướng dẫn HS đặt tay đúng hàng phím cơ sở và gõ bằng mười ngón; HS gõ một đoạn ngắn cho sẵn, tự đếm số lỗi
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV chiếu hai ảnh tư thế ngồi máy: một đúng, một sai; HS chỉ ra chỗ khác nhau ở lưng, khoảng cách mắt</t>
         </is>
       </c>
     </row>
@@ -32061,7 +32400,9 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>AI-NB (Nhận biết): Chỉ cho HS thấy phần trả lời tóm tắt do máy tự sinh đặt ở đầu trang kết quả.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV hướng dẫn HS chọn từ khoá ngắn, đúng trọng tâm cho một câu hỏi cụ thể; HS gõ từ khoá
+Năng lực số Miền 1 (Cơ bản, bậc 2): HS đối chiếu thông tin tìm được ở ít nhất hai trang và với SGK; ghi lại tên trang đã lấy thông tin vào phiếu để biết mình đang tin vào nguồn nào.
+Năng lực số Miền 6 (Cơ bản, bậc 2): GV chỉ cho HS thấy phần trả lời tóm tắt do máy tự sinh đặt ở đầu trang kết quả; nêu rõ đó là do trí tuệ nhân tạo viết</t>
         </is>
       </c>
     </row>
@@ -32181,7 +32522,8 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Cho HS quan sát cửa sổ giấy phép hiện ra khi cài một phần mềm, chỉ chỗ ghi phần mềm dùng miễn phí hay phải mua.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV cho HS quan sát cửa sổ giấy phép hiện ra khi cài một phần mềm, chỉ chỗ ghi phần mềm dùng miễn phí hay phải mua
+Năng lực số Miền 3 (Cơ bản, bậc 2): GV nêu công sức của người viết phần mềm, người vẽ tranh, người viết truyện; HS liên hệ với sản phẩm của chính mình: nếu bài mình làm bị bạn lấy đem nộp thì…</t>
         </is>
       </c>
     </row>
@@ -32276,7 +32618,8 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>NLS-ST (Cơ bản 2): Cho HS so sánh hai trang chiếu cùng nội dung.</t>
+          <t>Năng lực số Miền 3 (Cơ bản, bậc 2): GV cho HS so sánh hai trang chiếu cùng nội dung: một trang chữ nhỏ, nhiều màu loè loẹt và một trang chữ to, màu tương phản rõ
+Năng lực số Miền 3 (Cơ bản, bậc 2): HS định dạng lại bài trình chiếu của mình: chỉnh cỡ chữ tiêu đề và nội dung, chọn màu chữ nổi trên nền, căn lề cho thẳng, bỏ bớt chữ thừa.</t>
         </is>
       </c>
     </row>
@@ -32640,7 +32983,8 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Chọn phần mềm trò chơi mang tính học tập (xếp hình, luyện gõ, giải đố, tìm đường).</t>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): GV chọn phần mềm trò chơi mang tính học tập (xếp hình, luyện gõ, giải đố, tìm đường); HS chơi và nêu trò chơi đó rèn cho mình kĩ năng gì
+Năng lực số Miền 2 (Cơ bản, bậc 2): HS thoả thuận với bạn luật chơi và thứ tự lượt khi dùng chung một máy; giữ thái độ vui vẻ khi thắng, bình tĩnh khi thua, không tranh giành chuột và bàn phím.</t>
         </is>
       </c>
     </row>
@@ -32700,7 +33044,8 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Giới thiệu màn hình phần mềm lập trình trực quan.</t>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): GV giới thiệu màn hình phần mềm lập trình trực quan: khu vực khối lệnh, khu vực ghép lệnh, sân khấu và nhân vật; HS kéo thả vài khối lệnh di chuyển, xoay
+Năng lực số Miền 5 (Cơ bản, bậc 2): HS thử đổi thứ tự các khối lệnh rồi chạy lại để thấy máy làm đúng theo thứ tự mình xếp — sai ở đâu sửa ở đó, chạy lại không tốn gì.</t>
         </is>
       </c>
     </row>
@@ -32764,7 +33109,9 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>NLS-ST (Cơ bản 2): HS diễn tả một ý tưởng của mình thành chương trình cho “Tạo chương trình máy tính để diễn tả ý tưởng”.</t>
+          <t>Năng lực số Miền 3 (Cơ bản, bậc 2): HS diễn tả một ý tưởng của mình thành chương trình cho “Tạo chương trình máy tính để diễn tả ý tưởng”: chọn nhân vật, phông nền
+Năng lực số Miền 5 (Cơ bản, bậc 2): Khi chương trình chạy chưa đúng, HS chia nhỏ để tìm lỗi: chạy từng phần, kiểm tra thứ tự lệnh, đổi giá trị thời gian và bước đi
+Năng lực số Miền 2 (Cơ bản, bậc 2): HS giới thiệu chương trình của mình trước lớp, nghe bạn góp ý và ghi lại một điều mình sẽ cải tiến ở lần sau.</t>
         </is>
       </c>
     </row>
@@ -33229,7 +33576,8 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở bài “Vật liệu và dụng cụ trồng hoa, cây cảnh trong chậu”, GV chiếu ảnh phóng to từng loại giá thể.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài “Vật liệu và dụng cụ trồng hoa, cây cảnh trong chậu”, GV chiếu ảnh phóng to từng loại giá thể, phân bón, chậu và dụng cụ như xẻng nhỏ, bình tưới
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV chiếu vài tình huống trồng cây trong chậu và cho HS chọn bộ vật liệu, dụng cụ phù hợp cho từng loại cây; máy báo đúng
 KNS: KN lao động tự phục vụ: làm việc cẩn thận, kiên trì hoàn thành sản phẩm.</t>
         </is>
       </c>
@@ -33411,7 +33759,8 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở bài “Chậu hoa và cây cảnh mini”, GV chiếu ảnh phóng to nhiều kiểu chậu mini.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài “Chậu hoa và cây cảnh mini”, GV chiếu ảnh phóng to nhiều kiểu chậu mini cùng loại cây phù hợp với từng chậu; HS gọi tên cây
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV chiếu vài tình huống chọn chậu và cây cho góc học tập, ban công, lớp học; HS chọn phương án phù hợp rồi giải thích theo điều kiện ánh sáng, không gian
 KNS: KN lao động tự phục vụ: làm việc cẩn thận, kiên trì hoàn thành sản phẩm.</t>
         </is>
       </c>
@@ -33952,7 +34301,8 @@
       <c r="H33" s="4" t="inlineStr">
         <is>
           <t>NLS-ST: Tìm tư liệu, xem video hướng dẫn kĩ thuật; tạo sản phẩm và chụp/quay lại quá trình (có hướng dẫn).
-NLS-KT (Cơ bản 2): Ở hoạt động Khởi động bài “Làm đèn lồng”, GV chiếu đoạn phim ngắn về phố đèn lồng.
+Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Khởi động bài “Làm đèn lồng”, GV chiếu đoạn phim ngắn về phố đèn lồng và ảnh chụp gần vài mẫu đèn, phóng to chỗ nan và chỗ dán
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở hoạt động Thực hành, GV chiếu lại video ở đúng bước nhiều bạn còn lúng túng và dừng hình; HS đối chiếu sản phẩm của mình với hình để tìm ra chỗ nan…
 KNS: KN lao động tự phục vụ: làm việc cẩn thận, kiên trì hoàn thành sản phẩm.</t>
         </is>
       </c>
@@ -34018,7 +34368,8 @@
       <c r="H35" s="4" t="inlineStr">
         <is>
           <t>NLS-ST: Tìm tư liệu, xem video hướng dẫn kĩ thuật; tạo sản phẩm và chụp/quay lại quá trình (có hướng dẫn).
-NLS-GQVĐ (Cơ bản 2): Ở hoạt động Thực hành, khi chuồn chuồn chưa đứng được, GV chiếu lại hình dừng ở phần mỏ.
+Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Khởi động bài “Làm chuồn chuồn thăng bằng”, GV chiếu ảnh chụp gần chuồn chuồn tre đang đậu trên đầu ngón tay và video quay chậm lúc đặt thăng bằng
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở hoạt động Thực hành, khi chuồn chuồn chưa đứng được, GV chiếu lại hình dừng ở phần mỏ và cánh
 KNS: KN lao động tự phục vụ: làm việc cẩn thận, kiên trì hoàn thành sản phẩm.</t>
         </is>
       </c>
@@ -34330,7 +34681,9 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+          <t>Năng lực số Miền 3 (Cơ bản, bậc 2): Ở tiết Vận dụng – Sáng tạo tổng kết chủ đề “Âm thanh ngày mới”, mỗi nhóm dàn dựng tiết mục hát kết hợp gõ đệm và vận động
+Năng lực số Miền 2 (Cơ bản, bậc 2): Cả lớp xem lại bản quay và nhận xét theo ba tiêu chí chiếu sẵn trên màn hình: hát đúng giai điệu, gõ đệm đúng phách, vận động khớp nhạc
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -34463,7 +34816,9 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở tiết tổng kết chủ đề “Giai điệu quê hương”, GV mở bản thu các bài đã học và một vài trích đoạn dân ca cùng vùng miền; HS nghe đoán tên bài
+Năng lực số Miền 3 (Cơ bản, bậc 2): Các nhóm dàn dựng tiết mục hát kết hợp gõ đệm, vận động; GV quay lại rồi chiếu cho cả lớp xem
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -34599,7 +34954,9 @@
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở tiết tổng kết chủ đề “Thầy cô với chúng em”, GV mở bản thu các bài đã học trong chủ đề cho HS nghe đoán tên bài và nhắc lại nét giai điệu…
+Năng lực số Miền 3 (Cơ bản, bậc 2): Các nhóm dàn dựng tiết mục hát kết hợp gõ đệm và vận động; GV quay lại rồi chiếu cho cả lớp xem
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -34731,7 +35088,9 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Khởi động tổng kết chủ đề “Vui đón Tết”, GV mở lần lượt các đoạn giai điệu đã học từ học liệu số cho HS nghe đoán tên bài
+Năng lực số Miền 3 (Cơ bản, bậc 2): Ở phần Vận dụng – Sáng tạo, GV quay lại tiết mục mừng xuân của từng nhóm bằng điện thoại rồi chiếu lên tivi; các nhóm tự xem lại phần hát, gõ đệm
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -34931,7 +35290,9 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Khởi động tổng kết chủ đề “Thiên nhiên tươi đẹp”, GV mở lần lượt các đoạn giai điệu đã học từ học liệu số cho HS nghe đoán tên bài
+Năng lực số Miền 3 (Cơ bản, bậc 2): Ở phần Vận dụng – Sáng tạo, GV quay tiết mục của từng nhóm bằng điện thoại rồi chiếu lên tivi; các nhóm tự xem lại phần hát, gõ đệm
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -35031,7 +35392,12 @@
           <t>25</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Khám phá chủ đề “Tình bạn tuổi thơ”, GV chiếu hình tiết tấu lên màn hình và mở bản gõ mẫu từ học liệu số
+Năng lực số Miền 3 (Cơ bản, bậc 2): Ở phần Luyện tập, GV ghi âm phần hoà tấu của từng nhóm rồi mở lại cho cả lớp nghe; các nhóm tự nhận ra chỗ vào nhạc chưa khớp</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -35063,7 +35429,9 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Khởi động tổng kết chủ đề “Tình bạn tuổi thơ”, GV mở lần lượt các đoạn giai điệu đã học từ học liệu số cho HS nghe đoán tên bài
+Năng lực số Miền 3 (Cơ bản, bậc 2): Ở phần Vận dụng – Sáng tạo, GV quay tiết mục của từng nhóm rồi chiếu lên tivi; các nhóm tự xem lại phần hát, gõ đệm
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>
@@ -35199,7 +35567,9 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Khởi động tổng kết chủ đề “Âm nhạc nước ngoài”, GV mở lần lượt các đoạn giai điệu đã học từ học liệu số cho HS nghe đoán tên bài
+Năng lực số Miền 3 (Cơ bản, bậc 2): Ở phần Vận dụng – Sáng tạo, GV quay tiết mục của từng nhóm rồi chiếu lên tivi; các nhóm tự xem lại phần hát, gõ đệm
+KNS: KN tự tin biểu diễn trước tập thể và phối hợp cùng nhóm.</t>
         </is>
       </c>
     </row>

--- a/assets/docs/lop4/KHDH ca khoi - Lop 4.xlsx
+++ b/assets/docs/lop4/KHDH ca khoi - Lop 4.xlsx
@@ -28679,7 +28679,8 @@
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở phần kĩ năng của bài Unit 6 Our school facilities, GV mở tệp ghi âm.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần kĩ năng của bài Unit 6 Our school facilities, GV mở tệp ghi âm và chiếu tranh kèm từ khoá; HS nghe lần một nắm ý chung
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV mở bài hát của bài học trên màn hình cho cả lớp hát theo, sau đó ghi âm lượt hỏi đáp của vài cặp về phòng chức năng và mở lại để các…
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -28748,7 +28749,9 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 7 Our timetables, GV chiếu thời khoá biểu mẫu kèm tệp ghi âm mẫu; HS nghe rồi chỉ đúng môn học ở đúng thứ trên bảng
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu thời khoá biểu trống của lớp; từng cặp HS hỏi đáp bằng tiếng Anh rồi đọc để thầy cô điền
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -28782,7 +28785,9 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần luyện tập bài Unit 7, GV mở bài hát của bài học trên màn hình cho cả lớp hát theo rồi ghi âm lượt hỏi đáp về thời khoá biểu của vài…
+Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi nhóm làm một thời khoá biểu bằng hình: chọn biểu tượng môn học, ghi thứ và viết hai câu tiếng Anh giới thiệu ngày mình thích nhất
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -28816,7 +28821,8 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Mở bài tập tương tác nghe chọn tranh và điền tên môn còn thiếu vào thời khoá biểu.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài Unit 7 Our timetables, GV chiếu thời khoá biểu mẫu kèm tệp ghi âm; HS nghe rồi chỉ đúng môn học ở đúng thứ
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe chọn tranh và điền tên môn còn thiếu vào thời khoá biểu; máy chấm ngay nên HS nhận ra mình nghe nhầm môn nào
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -28885,7 +28891,9 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 7 Our timetables, GV chiếu thời khoá biểu mẫu kèm tệp ghi âm mẫu; HS nghe rồi chỉ đúng môn học ở đúng thứ trên bảng
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu thời khoá biểu trống của lớp; từng cặp HS hỏi đáp bằng tiếng Anh rồi đọc để thầy cô điền
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -28919,7 +28927,9 @@
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần luyện tập bài Unit 7, GV mở bài hát của bài học trên màn hình cho cả lớp hát theo rồi ghi âm lượt hỏi đáp về thời khoá biểu của vài…
+Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi nhóm làm một thời khoá biểu bằng hình: chọn biểu tượng môn học, ghi thứ và viết hai câu tiếng Anh giới thiệu ngày mình thích nhất
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -28953,7 +28963,8 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Vào bài Unit 8 My favourite subjects, GV chiếu bộ tranh các môn học.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 8 My favourite subjects, GV chiếu bộ tranh các môn học kèm tệp ghi âm mẫu; HS nghe rồi nối tên môn với tranh
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu bảng khảo sát môn học yêu thích của lớp; từng cặp HS hỏi đáp bằng tiếng Anh rồi đọc để thầy cô đánh dấu
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -29022,7 +29033,9 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần luyện tập bài Unit 8, GV mở bài tập tương tác nghe chọn tranh và điền tên môn còn thiếu vào câu
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV ghi âm lượt hỏi đáp về môn học yêu thích của vài cặp rồi mở cho cả lớp nghe; HS nhận xét theo tiêu chí nói đủ câu, phát âm rõ
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -29090,7 +29103,8 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Ở phần kĩ năng của bài Unit 8 My favourite subjects, GV mở bài tập tương tác nghe chọn tranh.
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần kĩ năng của bài Unit 8 My favourite subjects, GV mở bài tập tương tác nghe chọn tranh và điền tên môn còn thiếu vào câu
+Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi nhóm làm một trang giới thiệu môn học yêu thích: chọn hình, ghi tên môn và viết hai câu nêu lí do bằng tiếng Anh
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -29125,7 +29139,9 @@
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 8 My favourite subjects, GV chiếu bộ tranh các môn học kèm tệp ghi âm mẫu; HS nghe rồi nối tên môn với tranh
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu bảng khảo sát môn học yêu thích của lớp; từng cặp HS hỏi đáp bằng tiếng Anh rồi đọc để thầy cô đánh dấu
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -29159,7 +29175,9 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 9 Our sports day, GV chiếu bộ tranh các môn thể thao trong ngày hội thể thao kèm tệp ghi âm mẫu; HS nghe rồi nối tên môn với tranh
+Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu bảng đăng kí môn thi của lớp trong ngày hội thể thao; từng cặp HS hỏi đáp bằng tiếng Anh rồi đọc để thầy cô điền
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>

--- a/assets/docs/lop4/KHDH ca khoi - Lop 4.xlsx
+++ b/assets/docs/lop4/KHDH ca khoi - Lop 4.xlsx
@@ -9752,7 +9752,7 @@
       <c r="D4" s="4" t="inlineStr"/>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Kiến thức chung &amp; Chủ đề 1: Đội hình đội ngũ — Bài 1: Đi đều vòng bên phải (Tiết 1)</t>
+          <t>Chủ đề 1: Đội hình đội ngũ — Bài 1: Đi đều vòng bên phải (Tiết 1)</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -9837,8 +9837,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS đọc được sơ đồ đường di chuyển của “Đi đều vòng bên trái” và dự đoán đúng vị trí tổ mình.
-KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
+          <t>KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
     </row>
@@ -9906,8 +9905,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Đi đều vòng sau” với động tác mẫu trong clip.
-KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
+          <t>KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
     </row>
@@ -10010,8 +10008,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 2.5 CB2a: HS xin phép bạn trước khi chiếu clip và tự xoá clip sau tiết học.
-KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
+          <t>KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
     </row>
@@ -10045,8 +10042,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Động tác vươn thở và động tác tay với vòng” với động tác mẫu trong clip.
-KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
+          <t>KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
     </row>
@@ -10080,9 +10076,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu video mẫu động tác chân với vòng của chủ đề Bài tập thể dục, cho chạy chậm và dừng hình ở nhịp khuỵu gối và nhịp đưa vòng
-Năng lực số Miền 5 (Cơ bản, bậc 2): GV quay một lượt tập của từng tổ rồi chiếu lại; HS tự chấm theo ba tiêu chí chiếu sẵn là đúng nhịp, đủ biên độ, giữ vòng chắc
-KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
+          <t>KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
     </row>
@@ -10185,9 +10179,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu video mẫu động tác nhảy và động tác điều hoà với vòng, cho chạy chậm và dừng hình ở nhịp bật nhảy, nhịp thả lỏng
-Năng lực số Miền 5 (Cơ bản, bậc 2): GV quay một lượt tập của từng tổ rồi chiếu lại; HS tự chấm theo tiêu chí chiếu sẵn là bật đúng nhịp, tiếp đất êm, thả lỏng đủ chậm
-KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
+          <t>KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
     </row>
@@ -10221,8 +10213,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.2 CB2a: HS quay và xem chậm được clip mình thực hiện “Hoàn thiện bài thể dục với vòng”, tự chỉ ra lỗi của mình và của bạn.
-KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
+          <t>KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
     </row>
@@ -10392,11 +10383,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS điền và đọc được bảng theo dõi phần đội hình đội ngũ và bài thể dục với vòng, tự xác định nội dung cần cố gắng thêm.</t>
-        </is>
-      </c>
+      <c r="H22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -10463,7 +10450,7 @@
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.2 CB2a: HS quay và xem chậm được clip mình thực hiện “Hoàn thiện bài thể dục với vòng”, tự chỉ ra lỗi của mình và của bạn.</t>
+          <t>Năng lực số 3.2 CB2a: HS quay và xem chậm được clip mình thực hiện “Động tác nhảy, động tác điều hoà với vòng”, tự chỉ ra lỗi của mình và của bạn.</t>
         </is>
       </c>
     </row>
@@ -10495,11 +10482,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS điền và đọc được bảng theo dõi phần đội hình đội ngũ và bài thể dục với vòng, tự xác định nội dung cần cố gắng thêm.</t>
-        </is>
-      </c>
+      <c r="H25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -10638,8 +10621,7 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Động tác tại chỗ dẫn bóng” với động tác mẫu trong clip.
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -10673,8 +10655,7 @@
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS đọc được sơ đồ đường di chuyển của “Dẫn bóng theo hình chữ V, dẫn bóng vượt chướng ngại vật” và dự đoán đúng vị trí tổ mình.
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -10742,7 +10723,7 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Bài tập rèn luyện bật xa tại chỗ” với động tác mẫu trong clip.
+          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Bài tập rèn luyện kĩ năng bật xa” với động tác mẫu trong clip.
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -10882,8 +10863,7 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Động tác chuyền, bắt bóng bật đất bằng hai tay trước ngực” với động tác mẫu trong clip.
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -10949,11 +10929,7 @@
           <t>35</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>NLS-ST (Cơ bản 2): HS làm việc theo cặp với một máy GV giao cho mỗi tổ: một bạn quay 10 giây lúc bạn kia thực.</t>
-        </is>
-      </c>
+      <c r="H38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -10983,11 +10959,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS điền và đọc được bảng theo dõi phần hệ thống đội hình đội ngũ, bài thể dục với vòng và bóng rổ, tự xác định nội dung cần cố gắng thêm.</t>
-        </is>
-      </c>
+      <c r="H39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -11019,7 +10991,7 @@
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Bài tập rèn luyện bật xa tại chỗ” với động tác mẫu trong clip.
+          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Bài tập rèn luyện kĩ năng bật cao” với động tác mẫu trong clip.
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -11054,8 +11026,8 @@
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức bài ôn và nâng cao bài tập thăng bằng, GV chiếu trên tivi video kĩ thuật, cho chạy chậm và dừng ở tư thế dang tay
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay lượt tập của vài HS rồi chiếu chậm; cả nhóm cùng chỉ ra lỗi hay gặp như cúi đầu nhìn chân, tay buông xuôi
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức bài “Ôn bật cao, bật cao có đà ngắn”, GV chiếu trên tivi video kĩ thuật, cho chạy chậm và dừng ở chỗ lấy đà
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV chiếu bảng thành tích bật cao của các nhóm sau mỗi lượt; các nhóm nhìn bảng thấy mình tiến bộ bao nhiêu rồi bàn cách lấy đà ngắn hơn
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -11090,8 +11062,8 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần bài tập bổ trợ bật xa, GV chiếu trên tivi video kĩ thuật, cho chạy chậm và dừng ở chỗ khuỵu gối lấy đà, đánh tay và tiếp đất bằng hai chân
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV chiếu bảng thành tích bật xa của các nhóm lên tivi sau mỗi lượt; các nhóm nhìn bảng để thấy mình tiến bộ bao nhiêu và bàn cách lấy…
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần bài tập bổ trợ sức bật, GV chiếu trên tivi sơ đồ sân chơi kèm mũi tên chỉ đường di chuyển và vạch bật của từng đội
+Năng lực số Miền 5 (Cơ bản, bậc 2): Sau mỗi lượt, GV chiếu bảng kết quả các đội kèm số lần bật chưa qua vạch; các nhóm nhìn bảng tìm ra mình yếu ở khâu lấy đà hay khâu vươn người rồi…
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -11126,8 +11098,7 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 6.1 CB2a: HS đọc được nhận xét của ứng dụng về “Ôn ném rổ một tay trên vai.
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -11161,8 +11132,7 @@
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS tra và ghi được 3 điều luật liên quan đến “bóng rổ”, nêu rõ lấy từ nguồn nào.
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -11230,7 +11200,7 @@
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Bài tập rèn luyện thăng bằng” với động tác mẫu trong clip.
+          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Nhảy dây chụm hai chân” với động tác mẫu trong clip.
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -11265,8 +11235,7 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức bài ôn và nâng cao bài tập thăng bằng, GV chiếu trên tivi video kĩ thuật, cho chạy chậm và dừng ở tư thế dang tay
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV quay lượt tập của vài HS rồi chiếu chậm; cả nhóm cùng chỉ ra lỗi hay gặp như cúi đầu nhìn chân, tay buông xuôi
+          <t>Năng lực số 5.2 CB2b: HS bấm giờ, đếm và ghi được số liệu buổi tập “nhảy dây theo nhịp” của tổ mình.
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -11301,8 +11270,8 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần bài tập bổ trợ thăng bằng, GV chiếu trên tivi sơ đồ sân chơi nhìn từ trên xuống kèm mũi tên chỉ đường di chuyển của từng đội
-Năng lực số Miền 5 (Cơ bản, bậc 2): Sau mỗi lượt chơi, GV chiếu bảng kết quả các đội lên tivi kèm số lần mất thăng bằng; các nhóm nhìn bảng để tìm ra mình hay ngã ở đoạn nào và bàn…
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần trò chơi nhảy dây, GV chiếu trên tivi video mẫu, cho chạy chậm ở chỗ cổ tay quay dây và thời điểm bật nhảy
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần thi nhảy dây, GV chiếu bảng kết quả các nhóm lên tivi sau mỗi lượt kèm số lần vướng dây
 KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
@@ -11337,8 +11306,7 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Bài tập rèn luyện bật xa tại chỗ” với động tác mẫu trong clip.
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -11372,8 +11340,7 @@
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS điền và đọc được bảng theo dõi phần bật xa tại chỗ, tự xác định nội dung cần cố gắng thêm.
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -11407,9 +11374,7 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần bài tập bổ trợ bật xa, GV chiếu trên tivi video kĩ thuật, cho chạy chậm và dừng ở chỗ khuỵu gối lấy đà, đánh tay và tiếp đất bằng hai chân
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV chiếu bảng thành tích bật xa của các nhóm lên tivi sau mỗi lượt; các nhóm nhìn bảng để thấy mình tiến bộ bao nhiêu và bàn cách lấy…
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -11507,7 +11472,7 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Bài tập rèn luyện bật cao tại chỗ” với động tác mẫu trong clip.</t>
+          <t>Năng lực số 2.5 CB2a: HS xin phép bạn trước khi chiếu clip và tự xoá clip sau tiết học.</t>
         </is>
       </c>
     </row>
@@ -11539,12 +11504,7 @@
           <t>52</t>
         </is>
       </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Hình thành kiến thức bài “Ôn bật cao, bật cao có đà ngắn”, GV chiếu trên tivi video kĩ thuật, cho chạy chậm và dừng ở chỗ lấy đà
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Luyện tập, GV chiếu bảng thành tích bật cao của các nhóm sau mỗi lượt; các nhóm nhìn bảng thấy mình tiến bộ bao nhiêu rồi bàn cách lấy đà ngắn hơn</t>
-        </is>
-      </c>
+      <c r="H55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -11574,12 +11534,7 @@
           <t>53</t>
         </is>
       </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần bài tập bổ trợ sức bật, GV chiếu trên tivi sơ đồ sân chơi kèm mũi tên chỉ đường di chuyển và vạch bật của từng đội
-Năng lực số Miền 5 (Cơ bản, bậc 2): Sau mỗi lượt, GV chiếu bảng kết quả các đội kèm số lần bật chưa qua vạch; các nhóm nhìn bảng tìm ra mình yếu ở khâu lấy đà hay khâu vươn người rồi…</t>
-        </is>
-      </c>
+      <c r="H56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -11611,7 +11566,7 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS đọc được sơ đồ đường di chuyển của “Dẫn bóng theo hình chữ V, dẫn bóng vượt chướng ngại vật” và dự đoán đúng vị trí tổ mình.</t>
+          <t>Năng lực số 1.1 CB2c: HS nêu được điểm khác nhau giữa cách mình thực hiện “Động tác tại chỗ dẫn bóng” với động tác mẫu trong clip.</t>
         </is>
       </c>
     </row>
@@ -11643,11 +11598,7 @@
           <t>55</t>
         </is>
       </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>NLS-GQVĐ (Cơ bản 2): HS làm việc theo tổ với một đồng hồ bấm giờ GV giao.</t>
-        </is>
-      </c>
+      <c r="H58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -11679,7 +11630,7 @@
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB2b: HS bấm giờ, đếm và ghi được số liệu buổi tập “nhảy dây theo nhịp” của tổ mình.</t>
+          <t>Năng lực số 1.1 CB2c: HS đọc được sơ đồ đường di chuyển của “Dẫn bóng theo hình chữ V, dẫn bóng vượt chướng ngại vật” và dự đoán đúng vị trí tổ mình.</t>
         </is>
       </c>
     </row>
@@ -11711,11 +11662,7 @@
           <t>57</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS điền và đọc được bảng theo dõi phần các kĩ năng vận động cơ bản của chủ đề, tự xác định nội dung cần cố gắng thêm.</t>
-        </is>
-      </c>
+      <c r="H60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -11745,11 +11692,7 @@
           <t>58</t>
         </is>
       </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS điền và đọc được bảng theo dõi phần bóng rổ, thăng bằng và bật xa, tự xác định nội dung cần cố gắng thêm.</t>
-        </is>
-      </c>
+      <c r="H61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -11845,7 +11788,7 @@
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Ở phần Luyện tập, GV quay lượt tập trên cạn của vài.</t>
+          <t>Năng lực số 2.5 CB2a: HS xin phép bạn trước khi chiếu clip và tự xoá clip sau tiết học.</t>
         </is>
       </c>
     </row>
@@ -11877,11 +11820,7 @@
           <t>62</t>
         </is>
       </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.1 CB2a: HS nêu được điểm khác nhau giữa cách mình thực hiện “Động tác tay kiểu bơi ếch (mô phỏng/tập trên cạn)” với động tác mẫu trong clip.</t>
-        </is>
-      </c>
+      <c r="H65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -11977,7 +11916,7 @@
       </c>
       <c r="H68" s="4" t="inlineStr">
         <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Ở phần Luyện tập, GV quay lượt tập của vài.</t>
+          <t>Năng lực số 6.1 CB2a: HS đọc được nhận xét của ứng dụng về “Ôn ném rổ một tay trên vai.</t>
         </is>
       </c>
     </row>
@@ -12009,11 +11948,7 @@
           <t>66</t>
         </is>
       </c>
-      <c r="H69" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 1.1 CB2c: HS mô tả được đường đi của tay, chân trong “bơi ếch và an toàn dưới nước” nhờ clip quay dưới mặt nước.</t>
-        </is>
-      </c>
+      <c r="H69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -12043,11 +11978,7 @@
           <t>67</t>
         </is>
       </c>
-      <c r="H70" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS điền và đọc được bảng theo dõi phần hệ thống các chủ đề đã học, tự xác định nội dung cần cố gắng thêm.</t>
-        </is>
-      </c>
+      <c r="H70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -12137,11 +12068,7 @@
           <t>70</t>
         </is>
       </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB2b: HS lập được nhật kí vận động gắn với các chủ đề đã học trong năm và tự điều chỉnh kế hoạch sau một tuần.</t>
-        </is>
-      </c>
+      <c r="H73" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -21959,11 +21886,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
-        <is>
-          <t>NLS-GT (Cơ bản 2): HS cùng xây dựng bản quy ước sử dụng phòng máy và bảng phân công trực nhật, mỗi tổ theo dõi và.</t>
-        </is>
-      </c>
+      <c r="H20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -22246,11 +22169,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
-        <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Cho HS quan sát các cách tiêu tiền trên môi trường số: mua hàng qua mạng, nạp tiền vào trò chơi, mua.</t>
-        </is>
-      </c>
+      <c r="H29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -24817,11 +24736,7 @@
           <t>70</t>
         </is>
       </c>
-      <c r="H73" s="4" t="inlineStr">
-        <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Tổng kết môn học, GV chiếu sơ đồ các chủ đề đã học trong năm lên màn hình, mở.</t>
-        </is>
-      </c>
+      <c r="H73" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -25608,11 +25523,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>NLS-KT (Cơ bản 2): Cho HS tham quan “Sông Hồng và văn minh Sông Hồng” qua bảo tàng số, ảnh 360 độ.</t>
-        </is>
-      </c>
+      <c r="H25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -26135,11 +26046,7 @@
           <t>39</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>NLS-KT (Cơ bản 2): Ở hoạt động Khám phá bài “Dân cư và hoạt động sản xuất ở vùng Bắc Trung Bộ và Nam Trung Bộ”.</t>
-        </is>
-      </c>
+      <c r="H42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -26286,11 +26193,7 @@
           <t>44</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>NLS-GT (Cơ bản 2): Ở hoạt động nhóm, GV chiếu bảng chung “Di sản – Nơi có – Nét đặc sắc”.</t>
-        </is>
-      </c>
+      <c r="H47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -28084,7 +27987,8 @@
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 2): Ở bài Unit 4 My birthday party, GV chiếu bộ tranh đồ vật.
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở bài Unit 4 My birthday party, GV chiếu bộ tranh đồ vật và hoạt động trong bữa tiệc kèm tệp ghi âm; HS nghe rồi nối từ với tranh
+Năng lực số Miền 5 (Cơ bản, bậc 2): GV mở bài tập tương tác nghe chọn tranh đúng và điền từ còn thiếu vào lời mời; máy chấm ngay nên HS nhận ra mình còn nhầm hai từ gần giống nhau
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -28437,7 +28341,12 @@
           <t>35</t>
         </is>
       </c>
-      <c r="H38" s="4" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở tiết Review 1 phần nghe và đọc, GV mở bộ bài tập tương tác tổng hợp các chủ điểm đã học; sau mỗi câu máy báo đúng
+Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu bảng tổng hợp từ vựng và mẫu câu của các bài đã học, bấm sáng dần từng nhóm; HS nhìn bảng để nhớ lại theo chủ điểm chứ không học rời rạc</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -28469,8 +28378,8 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 5 (Cơ bản, bậc 2): Ở tiết Review 1 phần nghe và đọc, GV mở bộ bài tập tương tác tổng hợp các chủ điểm đã học; sau mỗi câu máy báo đúng
-Năng lực số Miền 1 (Cơ bản, bậc 2): GV chiếu bảng tổng hợp từ vựng và mẫu câu của các bài đã học, bấm sáng dần từng nhóm; HS nhìn bảng để nhớ lại theo chủ điểm chứ không học rời rạc</t>
+          <t>Năng lực số Miền 2 (Cơ bản, bậc 2): Ở tiết Review 1 phần nói và viết, GV chiếu bảng ghi câu trả lời của các nhóm lên màn hình theo từng chủ điểm
+Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi nhóm làm một trang ôn tập nhỏ: chọn hình minh hoạ cho ba chủ điểm đã học, ghi từ khoá và một mẫu câu</t>
         </is>
       </c>
     </row>
@@ -28891,8 +28800,8 @@
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Vào bài Unit 7 Our timetables, GV chiếu thời khoá biểu mẫu kèm tệp ghi âm mẫu; HS nghe rồi chỉ đúng môn học ở đúng thứ trên bảng
-Năng lực số Miền 2 (Cơ bản, bậc 2): GV chiếu thời khoá biểu trống của lớp; từng cặp HS hỏi đáp bằng tiếng Anh rồi đọc để thầy cô điền
+          <t>Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần luyện tập bài Unit 7, GV mở bài hát của bài học trên màn hình cho cả lớp hát theo rồi ghi âm lượt hỏi đáp về thời khoá biểu của vài…
+Năng lực số Miền 3 (Cơ bản, bậc 2): Mỗi nhóm làm một thời khoá biểu bằng hình: chọn biểu tượng môn học, ghi thứ và viết hai câu tiếng Anh giới thiệu ngày mình thích nhất
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -29599,7 +29508,12 @@
           <t>68</t>
         </is>
       </c>
-      <c r="H71" s="4" t="inlineStr"/>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Listen and tick của Review 2, GV chiếu tranh lên màn hình và mở bản nghe năm tình huống giao tiếp, dừng sau mỗi tình huống để HS chọn đáp án
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV chiếu danh sách các bài hát từ Unit 6 đến Unit 10 kèm lời chạy trên màn hình để các nhóm chọn một bài và hát đồng thanh</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
@@ -29832,7 +29746,9 @@
       </c>
       <c r="H78" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Vocabulary của Unit 11 “My home”, GV chiếu tranh đồ vật trong nhà kèm từ và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Whispering, sau mỗi lượt truyền tin GV chiếu câu gốc lên màn hình; hai đội đối chiếu câu mình nói với câu gốc
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -29902,8 +29818,8 @@
       </c>
       <c r="H80" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Vocabulary của Unit 11 “My home”, GV chiếu tranh đồ vật trong nhà kèm từ và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Whispering, sau mỗi lượt truyền tin GV chiếu câu gốc lên màn hình; hai đội đối chiếu câu mình nói với câu gốc
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 11 “My home”, GV mở bản nghe mẫu âm của các chữ cái trong bài
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát My house có lời chạy trên màn hình cho cả lớp hát; sau đó chia hai nhóm hát nối tiếp theo phần lời đang sáng và nghe…
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -29974,8 +29890,8 @@
       </c>
       <c r="H82" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 11 “My home”, GV chiếu tranh các phòng trong nhà lên màn hình và mở bản nghe mẫu
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bản chant về ngôi nhà có chữ chạy theo nhịp; sau khi nghe, các nhóm sắp lại các thẻ từ chỉ phòng theo đúng thứ tự xuất hiện trong…
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 12 “Jobs”, GV chiếu tranh những người đang làm việc kèm tên nghề lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Guess the job, GV chiếu lần lượt ảnh một đồ vật gắn với nghề như ống nghe, thước thợ, bảng phấn
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -30118,7 +30034,9 @@
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 12 “Jobs”, GV mở bản nghe mẫu các từ chỉ nghề, cho nghe chậm rồi nghe lại tốc độ thường và chiếu chữ có đánh dấu…
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Lip-reading, GV chiếu từ chỉ nghề riêng cho bạn nhìn, bạn nói không thành tiếng để nhóm đoán
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -30188,8 +30106,8 @@
       </c>
       <c r="H88" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 12 “Jobs”, GV mở bản nghe mẫu các từ chỉ nghề, cho nghe chậm rồi nghe lại tốc độ thường và chiếu chữ có đánh dấu…
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Lip-reading, GV chiếu từ chỉ nghề riêng cho bạn nhìn, bạn nói không thành tiếng để nhóm đoán
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 13 “Appearance”, GV chiếu tranh các nhân vật với ngoại hình khác nhau và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Nhân vật – Đặc điểm ngoại hình”; các cặp hỏi đáp về nhân vật trong tranh rồi lên điền câu của mình
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -30260,84 +30178,84 @@
       </c>
       <c r="H90" s="4" t="inlineStr">
         <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 13 “Appearance”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu người được tả
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát What do your parents look like? có lời chạy trên màn hình cho cả lớp hát
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>Unit 13 — Appearance</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr"/>
+      <c r="D91" s="4" t="inlineStr"/>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>Unit 13 — Appearance — Lesson 2 (Describing people) – Tiết 1</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 13 “Appearance”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu người được tả
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát What do your parents look like? có lời chạy trên màn hình cho cả lớp hát
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>Unit 13 — Appearance</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr"/>
+      <c r="D92" s="4" t="inlineStr"/>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>Unit 13 — Appearance — Lesson 2 (Describing people) – Tiết 2</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
           <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 13 “Appearance”, GV mở bản nghe mẫu các câu mô tả ngoại hình
 Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi truyền tin, sau mỗi lượt GV chiếu câu gốc mô tả một người lên màn hình; hai đội đối chiếu câu mình nói với câu gốc
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="4" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>Unit 13 — Appearance</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr"/>
-      <c r="D91" s="4" t="inlineStr"/>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>Unit 13 — Appearance — Lesson 2 (Describing people) – Tiết 1</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G91" s="4" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="H91" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 13 “Appearance”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu người được tả
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát What do your parents look like? có lời chạy trên màn hình cho cả lớp hát
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="4" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B92" s="4" t="inlineStr">
-        <is>
-          <t>Unit 13 — Appearance</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr"/>
-      <c r="D92" s="4" t="inlineStr"/>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>Unit 13 — Appearance — Lesson 2 (Describing people) – Tiết 2</t>
-        </is>
-      </c>
-      <c r="F92" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G92" s="4" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="H92" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 13 “Appearance”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu người được tả
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát What do your parents look like? có lời chạy trên màn hình cho cả lớp hát
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
-        </is>
-      </c>
-    </row>
     <row r="93">
       <c r="A93" s="4" t="inlineStr">
         <is>
@@ -30404,8 +30322,8 @@
       </c>
       <c r="H94" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 13 “Appearance”, GV chiếu tranh các nhân vật với ngoại hình khác nhau và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Nhân vật – Đặc điểm ngoại hình”; các cặp hỏi đáp về nhân vật trong tranh rồi lên điền câu của mình
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Vocabulary của Unit 14 “Daily activities”, GV chiếu tranh các việc làm hằng ngày kèm từ mới lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Giờ – Việc em làm”; các cặp hỏi đáp về thời gian biểu của nhau rồi lên điền câu của mình
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -30476,82 +30394,84 @@
       </c>
       <c r="H96" s="4" t="inlineStr">
         <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Vocabulary của Unit 14 “Daily activities”, GV chiếu tranh các việc làm trong ngày kèm từ mới lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Change chairs, GV chiếu câu lệnh lên màn hình để cả lớp cùng đọc; HS nghe và đổi chỗ nếu câu đúng với mình
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Unit 14 — Daily activities</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr"/>
+      <c r="D97" s="4" t="inlineStr"/>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>Unit 14 — Daily activities — Lesson 2 (Frequency &amp; time) – Tiết 1</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Vocabulary của Unit 14 “Daily activities”, GV chiếu tranh các việc làm trong ngày kèm từ mới lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Change chairs, GV chiếu câu lệnh lên màn hình để cả lớp cùng đọc; HS nghe và đổi chỗ nếu câu đúng với mình
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>Unit 14 — Daily activities</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr"/>
+      <c r="D98" s="4" t="inlineStr"/>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>Unit 14 — Daily activities — Lesson 2 (Frequency &amp; time) – Tiết 2</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
           <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 14 “Daily activities”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu
 Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Spelling Bee, GV chiếu từ đã học lên màn hình rồi che đi, các nhóm đánh vần lại
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>Unit 14 — Daily activities</t>
-        </is>
-      </c>
-      <c r="C97" s="4" t="inlineStr"/>
-      <c r="D97" s="4" t="inlineStr"/>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>Unit 14 — Daily activities — Lesson 2 (Frequency &amp; time) – Tiết 1</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G97" s="4" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="H97" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Vocabulary của Unit 14 “Daily activities”, GV chiếu tranh các việc làm trong ngày kèm từ mới lên màn hình và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Change chairs, GV chiếu câu lệnh lên màn hình để cả lớp cùng đọc; HS nghe và đổi chỗ nếu câu đúng với mình
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="B98" s="4" t="inlineStr">
-        <is>
-          <t>Unit 14 — Daily activities</t>
-        </is>
-      </c>
-      <c r="C98" s="4" t="inlineStr"/>
-      <c r="D98" s="4" t="inlineStr"/>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>Unit 14 — Daily activities — Lesson 2 (Frequency &amp; time) – Tiết 2</t>
-        </is>
-      </c>
-      <c r="F98" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G98" s="4" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="H98" s="4" t="inlineStr">
-        <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
-        </is>
-      </c>
-    </row>
     <row r="99">
       <c r="A99" s="4" t="inlineStr">
         <is>
@@ -30618,8 +30538,8 @@
       </c>
       <c r="H100" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 14 “Daily activities”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Spelling Bee, GV chiếu từ đã học lên màn hình rồi che đi, các nhóm đánh vần lại
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 15 “My family's weekends”, GV chiếu tranh các địa điểm trong thị trấn kèm tên gọi lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Nơi đến cuối tuần – Việc làm ở đó”; các cặp hỏi đáp rồi lên điền câu của mình
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -30690,81 +30610,82 @@
       </c>
       <c r="H102" s="4" t="inlineStr">
         <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 15, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu nơi gia đình bạn nhỏ đến
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát Where do they go on Saturdays? có lời chạy trên màn hình cho cả lớp hát
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>Unit 15 — My family's weekends</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr"/>
+      <c r="D103" s="4" t="inlineStr"/>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>Unit 15 — My family's weekends — Lesson 2 (Family members' weekends) – Tiết 1</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>Unit 15 — My family's weekends</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr"/>
+      <c r="D104" s="4" t="inlineStr"/>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>Unit 15 — My family's weekends — Lesson 2 (Family members' weekends) – Tiết 2</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
           <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 15 “My family's weekends”, GV mở bản nghe mẫu, cho nghe chậm rồi nghe lại tốc độ thường và chiếu câu có đánh dấu trọng âm…
 Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Matching, GV chiếu hai cột từ và tranh bị xáo trộn; các nhóm nối thử rồi bấm kiểm tra
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="B103" s="4" t="inlineStr">
-        <is>
-          <t>Unit 15 — My family's weekends</t>
-        </is>
-      </c>
-      <c r="C103" s="4" t="inlineStr"/>
-      <c r="D103" s="4" t="inlineStr"/>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>Unit 15 — My family's weekends — Lesson 2 (Family members' weekends) – Tiết 1</t>
-        </is>
-      </c>
-      <c r="F103" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G103" s="4" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="H103" s="4" t="inlineStr">
-        <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="4" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="B104" s="4" t="inlineStr">
-        <is>
-          <t>Unit 15 — My family's weekends</t>
-        </is>
-      </c>
-      <c r="C104" s="4" t="inlineStr"/>
-      <c r="D104" s="4" t="inlineStr"/>
-      <c r="E104" s="4" t="inlineStr">
-        <is>
-          <t>Unit 15 — My family's weekends — Lesson 2 (Family members' weekends) – Tiết 2</t>
-        </is>
-      </c>
-      <c r="F104" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G104" s="4" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="H104" s="4" t="inlineStr">
-        <is>
-          <t>NLS-GQVĐ (Cơ bản 2): Ở phần Warm-up trò chơi Matching, GV chiếu hai cột từ.
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
-        </is>
-      </c>
-    </row>
     <row r="105">
       <c r="A105" s="4" t="inlineStr">
         <is>
@@ -30831,8 +30752,8 @@
       </c>
       <c r="H106" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 15 “My family's weekends”, GV chiếu tranh các địa điểm trong thị trấn kèm tên gọi lên màn hình và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Nơi đến cuối tuần – Việc làm ở đó”; các cặp hỏi đáp rồi lên điền câu của mình
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Listen and tick của Review 3, GV chiếu tranh lên màn hình và mở bản nghe các tình huống giao tiếp đã học, dừng sau mỗi tình huống để HS chọn
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát và bản chant của Unit 15 có lời chạy trên màn hình; các nhóm chọn một bài
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -30865,7 +30786,12 @@
           <t>104</t>
         </is>
       </c>
-      <c r="H107" s="4" t="inlineStr"/>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Fun time của Review 3, GV chiếu lần lượt các từ và câu đã học lên màn hình cho HS đọc nối tiếp
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần luyện tập, GV mở bài tập tương tác nối câu hỏi với câu trả lời; HS chọn rồi bấm kiểm tra</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="inlineStr">
@@ -31066,8 +30992,8 @@
       </c>
       <c r="H113" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 16 “Weather”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu kiểu thời tiết
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở phần Warm-up, GV mở bài hát What was the weather like? có lời chạy trên màn hình cho cả lớp hát
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 16 “Weather”, GV mở bản nghe mẫu hai âm được học, cho nghe chậm rồi nghe lại tốc độ thường và chiếu câu ví dụ có…
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Slap the board, GV chiếu các từ đã học lên màn hình; hai đội nghe GV đọc rồi lên chạm đúng từ
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -31138,8 +31064,8 @@
       </c>
       <c r="H115" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Vocabulary của Unit 16 “Weather”, GV chiếu tranh các kiểu thời tiết kèm từ mới lên màn hình và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Nơi – Thời tiết hôm nay – Câu nói bằng tiếng Anh”; các cặp hỏi đáp rồi lên điền
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 17 “In the city”, GV chiếu tranh các địa điểm trong thành phố kèm tên gọi lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Địa điểm – Việc làm ở đó”; các cặp hỏi đáp rồi lên điền câu của mình
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -31210,8 +31136,8 @@
       </c>
       <c r="H117" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 17 “In the city”, GV chiếu tranh các địa điểm trong thành phố kèm tên gọi lên màn hình và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Địa điểm – Việc làm ở đó”; các cặp hỏi đáp rồi lên điền câu của mình
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 17 “In the city”, GV chiếu sơ đồ đường phố lên màn hình và mở bản nghe mẫu các câu chỉ đường
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bản đồ khu phố có đánh dấu điểm xuất phát và đích đến; các cặp thay nhau chỉ đường bằng tiếng Anh
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -31282,7 +31208,9 @@
       </c>
       <c r="H119" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 17 “In the city”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu nơi được nhắc tới
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Memory game, GV chiếu bộ thẻ từ chỉ đường và địa điểm rồi giấu dần từng thẻ; các nhóm nhớ và gọi tên thẻ đã mất
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -31352,8 +31280,8 @@
       </c>
       <c r="H121" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 17 “In the city”, GV chiếu tranh các địa điểm trong thành phố kèm tên gọi lên màn hình và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Địa điểm – Việc làm ở đó”; các cặp hỏi đáp rồi lên điền câu của mình
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 18 “At the shopping centre”, GV chiếu tranh trung tâm mua sắm kèm tên các gian hàng và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Gian hàng – Thứ mua được ở đó”; các cặp hỏi đáp rồi lên điền câu của mình
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -31424,82 +31352,82 @@
       </c>
       <c r="H123" s="4" t="inlineStr">
         <is>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 18, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần ôn số, GV chiếu các số 20, 50, 80, 90 lên màn hình rồi yêu cầu HS thêm từ thousand và đọc to
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>Unit 18 — At the shopping centre</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr"/>
+      <c r="D124" s="4" t="inlineStr"/>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>Unit 18 — At the shopping centre — Lesson 2 (Prices &amp; buying) – Tiết 1</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>Unit 18 — At the shopping centre</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr"/>
+      <c r="D125" s="4" t="inlineStr"/>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>Unit 18 — At the shopping centre — Lesson 2 (Prices &amp; buying) – Tiết 2</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>1 tiết</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
           <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 18 “At the shopping centre”, GV mở bản nghe mẫu, cho nghe chậm rồi nghe lại tốc độ thường và chiếu câu có đánh dấu chỗ…
 Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Guess the price, GV chiếu ảnh món hàng cùng vài mức giá; các nhóm đoán giá bằng tiếng Anh rồi bấm chọn
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="4" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B124" s="4" t="inlineStr">
-        <is>
-          <t>Unit 18 — At the shopping centre</t>
-        </is>
-      </c>
-      <c r="C124" s="4" t="inlineStr"/>
-      <c r="D124" s="4" t="inlineStr"/>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>Unit 18 — At the shopping centre — Lesson 2 (Prices &amp; buying) – Tiết 1</t>
-        </is>
-      </c>
-      <c r="F124" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G124" s="4" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="H124" s="4" t="inlineStr">
-        <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="4" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B125" s="4" t="inlineStr">
-        <is>
-          <t>Unit 18 — At the shopping centre</t>
-        </is>
-      </c>
-      <c r="C125" s="4" t="inlineStr"/>
-      <c r="D125" s="4" t="inlineStr"/>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>Unit 18 — At the shopping centre — Lesson 2 (Prices &amp; buying) – Tiết 2</t>
-        </is>
-      </c>
-      <c r="F125" s="4" t="inlineStr">
-        <is>
-          <t>1 tiết</t>
-        </is>
-      </c>
-      <c r="G125" s="4" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="H125" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 18 “At the shopping centre”, GV mở bản nghe mẫu, cho nghe chậm rồi nghe lại tốc độ thường và chiếu câu có đánh dấu chỗ…
-Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Guess the price, GV chiếu ảnh món hàng cùng vài mức giá; các nhóm đoán giá bằng tiếng Anh rồi bấm chọn
-KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
-        </is>
-      </c>
-    </row>
     <row r="126">
       <c r="A126" s="4" t="inlineStr">
         <is>
@@ -31566,7 +31494,9 @@
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 19 “The animal world”, GV chiếu tranh các loài vật kèm tên gọi lên màn hình và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Con vật – Nơi sống – Đặc điểm”; các cặp hỏi đáp rồi lên điền câu của mình
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -31636,8 +31566,8 @@
       </c>
       <c r="H129" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 19 “The animal world”, GV chiếu tranh các loài vật kèm tên gọi lên màn hình và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Con vật – Nơi sống – Đặc điểm”; các cặp hỏi đáp rồi lên điền câu của mình
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and repeat của Unit 19 “The animal world”, GV chiếu tranh loài vật lên màn hình và mở bản nghe mẫu các câu mô tả
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi đoán con vật, GV chiếu ảnh bị che phần lớn; các nhóm đoán tên bằng tiếng Anh rồi giơ tay trả lời
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -31708,7 +31638,9 @@
       </c>
       <c r="H131" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 19, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu con vật được nhắc tới
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Con vật – Nơi sống – Thức ăn”; các cặp hỏi đáp rồi lên điền câu của mình
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -31778,8 +31710,8 @@
       </c>
       <c r="H133" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 19 “The animal world”, GV chiếu tranh các loài vật kèm tên gọi lên màn hình và mở bản nghe mẫu
-Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Con vật – Nơi sống – Đặc điểm”; các cặp hỏi đáp rồi lên điền câu của mình
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Look, listen and repeat của Unit 20 “At summer camp”, GV chiếu tranh các hoạt động ở trại hè kèm tên gọi và mở bản nghe mẫu
+Năng lực số Miền 2 (Cơ bản, bậc 2): Ở hoạt động luyện nói, GV chiếu bảng chung “Hoạt động ở trại hè – Vì sao em thích”; các cặp hỏi đáp rồi lên điền câu của mình
 KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
@@ -31850,7 +31782,9 @@
       </c>
       <c r="H135" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở hoạt động Listen and tick của Unit 20 “At summer camp”, GV chiếu tranh lên màn hình và mở bản nghe, dừng sau mỗi đoạn để HS đánh dấu
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần luyện tập, GV mở bài tập tương tác nối hoạt động với đồ dùng cần mang theo; HS chọn rồi bấm kiểm tra
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>
@@ -31990,7 +31924,9 @@
       </c>
       <c r="H139" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
+          <t>Năng lực số Miền 1 (Cơ bản, bậc 2): Ở phần Listen and tick của Review 4, GV chiếu tranh lên màn hình và mở bản nghe các tình huống đã học, dừng sau mỗi tình huống để HS chọn
+Năng lực số Miền 5 (Cơ bản, bậc 2): Ở phần Warm-up trò chơi Choose and throw, GV chiếu các phương án trả lời lên màn hình; hai đội chọn rồi ném bóng dính vào ô mình chọn
+KNS: KN giao tiếp: mạnh dạn chào hỏi, giới thiệu bản thân bằng câu đơn giản.</t>
         </is>
       </c>
     </row>

--- a/assets/docs/lop4/KHDH ca khoi - Lop 4.xlsx
+++ b/assets/docs/lop4/KHDH ca khoi - Lop 4.xlsx
@@ -12422,7 +12422,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 2.1 CB2a: HS nhập, đọc số liệu thi đua và nhận xét dựa trên kết quả thật của tổ mình.</t>
+          <t>Năng lực số 2.5 CB2a: HS nhận xét bạn bằng lời tích cực, cụ thể và biết cách góp ý tế nhị trên nhóm lớp.</t>
         </is>
       </c>
     </row>
@@ -12456,7 +12456,7 @@
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 2.5 CB2a: HS nhận xét bạn bằng lời tích cực, cụ thể và biết cách góp ý tế nhị trên nhóm lớp.</t>
+          <t>Năng lực số 2.1 CB2a: HS nhập, đọc số liệu thi đua và nhận xét dựa trên kết quả thật của tổ mình.</t>
         </is>
       </c>
     </row>
@@ -13117,7 +13117,7 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 2.1 CB2a: HS nhập, đọc số liệu thi đua và nhận xét dựa trên kết quả thật của tổ mình.</t>
+          <t>Năng lực số 1.1 CB2c: HS khảo sát, tổng hợp được số liệu về cảnh quan trường lớp và chỉ ra việc cần làm.</t>
         </is>
       </c>
     </row>
@@ -13151,7 +13151,7 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS khảo sát, tổng hợp được số liệu về cảnh quan trường lớp và chỉ ra việc cần làm.
+          <t>Năng lực số 2.1 CB2a: HS nhập, đọc số liệu thi đua và nhận xét dựa trên kết quả thật của tổ mình.
 KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
         </is>
       </c>
@@ -14962,7 +14962,7 @@
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 2.1 CB2a: HS nhập, đọc số liệu thi đua và nhận xét dựa trên kết quả thật của tổ mình.</t>
+          <t>Năng lực số 1.1 CB2c: HS xác định được vị trí cảnh quan địa phương trên bản đồ số và mô tả đặc điểm của nó.</t>
         </is>
       </c>
     </row>
@@ -14996,7 +14996,7 @@
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS xác định được vị trí cảnh quan địa phương trên bản đồ số và mô tả đặc điểm của nó.</t>
+          <t>Năng lực số 2.1 CB2a: HS nhập, đọc số liệu thi đua và nhận xét dựa trên kết quả thật của tổ mình.</t>
         </is>
       </c>
     </row>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="H104" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.1 CB2a: HS trình bày được sản phẩm giới thiệu nghề truyền thống và nêu rõ nguồn tư liệu.
+          <t>Năng lực số 1.1 CB2c: HS tìm hiểu và trình bày được các công đoạn của một nghề truyền thống, có ghi nguồn tư liệu.
 KNS: KN lao động tự phục vụ và bước đầu tìm hiểu nghề nghiệp.</t>
         </is>
       </c>
@@ -15620,7 +15620,7 @@
       </c>
       <c r="H105" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS tìm hiểu và trình bày được các công đoạn của một nghề truyền thống, có ghi nguồn tư liệu.
+          <t>Năng lực số 3.1 CB2a: HS trình bày được sản phẩm giới thiệu nghề truyền thống và nêu rõ nguồn tư liệu.
 KNS: KN lao động tự phục vụ và bước đầu tìm hiểu nghề nghiệp.</t>
         </is>
       </c>

--- a/assets/docs/lop4/KHDH ca khoi - Lop 4.xlsx
+++ b/assets/docs/lop4/KHDH ca khoi - Lop 4.xlsx
@@ -12162,7 +12162,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NHẬN DIỆN BẢN THÂN</t>
+          <t>Chủ đề: Nhận diện bản thân</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
@@ -12196,7 +12196,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NHẬN DIỆN BẢN THÂN</t>
+          <t>Chủ đề: Nhận diện bản thân</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
@@ -12231,7 +12231,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NHẬN DIỆN BẢN THÂN</t>
+          <t>Chủ đề: Nhận diện bản thân</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
@@ -12266,7 +12266,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NHẬN DIỆN BẢN THÂN</t>
+          <t>Chủ đề: Nhận diện bản thân</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
@@ -12296,7 +12296,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NHẬN DIỆN BẢN THÂN</t>
+          <t>Chủ đề: Nhận diện bản thân</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -12331,7 +12331,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NHẬN DIỆN BẢN THÂN</t>
+          <t>Chủ đề: Nhận diện bản thân</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NHẬN DIỆN BẢN THÂN</t>
+          <t>Chủ đề: Nhận diện bản thân</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -12400,7 +12400,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NHẬN DIỆN BẢN THÂN</t>
+          <t>Chủ đề: Nhận diện bản thân</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -12434,7 +12434,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NHẬN DIỆN BẢN THÂN</t>
+          <t>Chủ đề: Nhận diện bản thân</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
@@ -12468,7 +12468,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NHẬN DIỆN BẢN THÂN</t>
+          <t>Chủ đề: Nhận diện bản thân</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -12498,7 +12498,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NHẬN DIỆN BẢN THÂN</t>
+          <t>Chủ đề: Nhận diện bản thân</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -12532,7 +12532,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NHẬN DIỆN BẢN THÂN</t>
+          <t>Chủ đề: Nhận diện bản thân</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG VÀ TƯ DUY KHOA HỌC</t>
+          <t>Chủ đề: Nếp sống và tư duy khoa học</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -12596,7 +12596,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG VÀ TƯ DUY KHOA HỌC</t>
+          <t>Chủ đề: Nếp sống và tư duy khoa học</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG VÀ TƯ DUY KHOA HỌC</t>
+          <t>Chủ đề: Nếp sống và tư duy khoa học</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -12665,7 +12665,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG VÀ TƯ DUY KHOA HỌC</t>
+          <t>Chủ đề: Nếp sống và tư duy khoa học</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr"/>
@@ -12695,7 +12695,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG VÀ TƯ DUY KHOA HỌC</t>
+          <t>Chủ đề: Nếp sống và tư duy khoa học</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr"/>
@@ -12729,7 +12729,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG VÀ TƯ DUY KHOA HỌC</t>
+          <t>Chủ đề: Nếp sống và tư duy khoa học</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
@@ -12764,7 +12764,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG VÀ TƯ DUY KHOA HỌC</t>
+          <t>Chủ đề: Nếp sống và tư duy khoa học</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
@@ -12794,7 +12794,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG VÀ TƯ DUY KHOA HỌC</t>
+          <t>Chủ đề: Nếp sống và tư duy khoa học</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
@@ -12828,7 +12828,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG VÀ TƯ DUY KHOA HỌC</t>
+          <t>Chủ đề: Nếp sống và tư duy khoa học</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
@@ -12863,7 +12863,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG VÀ TƯ DUY KHOA HỌC</t>
+          <t>Chủ đề: Nếp sống và tư duy khoa học</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
@@ -12893,7 +12893,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG VÀ TƯ DUY KHOA HỌC</t>
+          <t>Chủ đề: Nếp sống và tư duy khoa học</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
@@ -12927,7 +12927,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: NẾP SỐNG VÀ TƯ DUY KHOA HỌC</t>
+          <t>Chủ đề: Nếp sống và tư duy khoa học</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr"/>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: YÊU TRƯỜNG, MẾN LỚP</t>
+          <t>Chủ đề: Yêu trường, mến lớp</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
@@ -12996,7 +12996,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: YÊU TRƯỜNG, MẾN LỚP</t>
+          <t>Chủ đề: Yêu trường, mến lớp</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr"/>
@@ -13030,7 +13030,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: YÊU TRƯỜNG, MẾN LỚP</t>
+          <t>Chủ đề: Yêu trường, mến lớp</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr"/>
@@ -13065,7 +13065,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: YÊU TRƯỜNG, MẾN LỚP</t>
+          <t>Chủ đề: Yêu trường, mến lớp</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr"/>
@@ -13095,7 +13095,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: YÊU TRƯỜNG, MẾN LỚP</t>
+          <t>Chủ đề: Yêu trường, mến lớp</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr"/>
@@ -13129,7 +13129,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: YÊU TRƯỜNG, MẾN LỚP</t>
+          <t>Chủ đề: Yêu trường, mến lớp</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: YÊU TRƯỜNG, MẾN LỚP</t>
+          <t>Chủ đề: Yêu trường, mến lớp</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
@@ -13198,7 +13198,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: YÊU TRƯỜNG, MẾN LỚP</t>
+          <t>Chủ đề: Yêu trường, mến lớp</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
@@ -13232,7 +13232,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: YÊU TRƯỜNG, MẾN LỚP</t>
+          <t>Chủ đề: Yêu trường, mến lớp</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr"/>
@@ -13267,7 +13267,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: YÊU TRƯỜNG, MẾN LỚP</t>
+          <t>Chủ đề: Yêu trường, mến lớp</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr"/>
@@ -13297,7 +13297,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: YÊU TRƯỜNG, MẾN LỚP</t>
+          <t>Chủ đề: Yêu trường, mến lớp</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr"/>
@@ -13331,7 +13331,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: YÊU TRƯỜNG, MẾN LỚP</t>
+          <t>Chủ đề: Yêu trường, mến lớp</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr"/>
@@ -13366,7 +13366,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ LỰC THỰC HIỆN NHIỆM VỤ</t>
+          <t>Chủ đề: Tự lực thực hiện nhiệm vụ</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
@@ -13396,7 +13396,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ LỰC THỰC HIỆN NHIỆM VỤ</t>
+          <t>Chủ đề: Tự lực thực hiện nhiệm vụ</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
@@ -13431,7 +13431,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ LỰC THỰC HIỆN NHIỆM VỤ</t>
+          <t>Chủ đề: Tự lực thực hiện nhiệm vụ</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr"/>
@@ -13466,7 +13466,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ LỰC THỰC HIỆN NHIỆM VỤ</t>
+          <t>Chủ đề: Tự lực thực hiện nhiệm vụ</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr"/>
@@ -13501,7 +13501,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ LỰC THỰC HIỆN NHIỆM VỤ</t>
+          <t>Chủ đề: Tự lực thực hiện nhiệm vụ</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr"/>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ LỰC THỰC HIỆN NHIỆM VỤ</t>
+          <t>Chủ đề: Tự lực thực hiện nhiệm vụ</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
@@ -13570,7 +13570,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ LỰC THỰC HIỆN NHIỆM VỤ</t>
+          <t>Chủ đề: Tự lực thực hiện nhiệm vụ</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr"/>
@@ -13604,7 +13604,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ LỰC THỰC HIỆN NHIỆM VỤ</t>
+          <t>Chủ đề: Tự lực thực hiện nhiệm vụ</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
@@ -13638,7 +13638,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ LỰC THỰC HIỆN NHIỆM VỤ</t>
+          <t>Chủ đề: Tự lực thực hiện nhiệm vụ</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr"/>
@@ -13673,7 +13673,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ LỰC THỰC HIỆN NHIỆM VỤ</t>
+          <t>Chủ đề: Tự lực thực hiện nhiệm vụ</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr"/>
@@ -13703,7 +13703,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ LỰC THỰC HIỆN NHIỆM VỤ</t>
+          <t>Chủ đề: Tự lực thực hiện nhiệm vụ</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr"/>
@@ -13737,7 +13737,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TỰ LỰC THỰC HIỆN NHIỆM VỤ</t>
+          <t>Chủ đề: Tự lực thực hiện nhiệm vụ</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr"/>
@@ -13772,7 +13772,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÁI ẤM GIA ĐÌNH</t>
+          <t>Chủ đề: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr"/>
@@ -13802,7 +13802,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÁI ẤM GIA ĐÌNH</t>
+          <t>Chủ đề: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr"/>
@@ -13836,7 +13836,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÁI ẤM GIA ĐÌNH</t>
+          <t>Chủ đề: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr"/>
@@ -13871,7 +13871,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÁI ẤM GIA ĐÌNH</t>
+          <t>Chủ đề: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr"/>
@@ -13905,7 +13905,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÁI ẤM GIA ĐÌNH</t>
+          <t>Chủ đề: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr"/>
@@ -13939,7 +13939,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: MÁI ẤM GIA ĐÌNH</t>
+          <t>Chủ đề: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr"/>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: PHÒNG TRÁNH BỊ XÂM HẠI</t>
+          <t>Chủ đề: Phòng tránh bị xâm hại</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr"/>
@@ -14209,7 +14209,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: PHÒNG TRÁNH BỊ XÂM HẠI</t>
+          <t>Chủ đề: Phòng tránh bị xâm hại</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr"/>
@@ -14244,7 +14244,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: PHÒNG TRÁNH BỊ XÂM HẠI</t>
+          <t>Chủ đề: Phòng tránh bị xâm hại</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr"/>
@@ -14279,7 +14279,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: PHÒNG TRÁNH BỊ XÂM HẠI</t>
+          <t>Chủ đề: Phòng tránh bị xâm hại</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr"/>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: PHÒNG TRÁNH BỊ XÂM HẠI</t>
+          <t>Chủ đề: Phòng tránh bị xâm hại</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr"/>
@@ -14349,7 +14349,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: PHÒNG TRÁNH BỊ XÂM HẠI</t>
+          <t>Chủ đề: Phòng tránh bị xâm hại</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr"/>
@@ -14384,7 +14384,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: PHÒNG TRÁNH BỊ XÂM HẠI</t>
+          <t>Chủ đề: Phòng tránh bị xâm hại</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr"/>
@@ -14418,7 +14418,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: PHÒNG TRÁNH BỊ XÂM HẠI</t>
+          <t>Chủ đề: Phòng tránh bị xâm hại</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
@@ -14453,7 +14453,7 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: PHÒNG TRÁNH BỊ XÂM HẠI</t>
+          <t>Chủ đề: Phòng tránh bị xâm hại</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr"/>
@@ -14488,7 +14488,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: PHÒNG TRÁNH BỊ XÂM HẠI</t>
+          <t>Chủ đề: Phòng tránh bị xâm hại</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr"/>
@@ -14523,7 +14523,7 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: PHÒNG TRÁNH BỊ XÂM HẠI</t>
+          <t>Chủ đề: Phòng tránh bị xâm hại</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr"/>
@@ -14558,7 +14558,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: PHÒNG TRÁNH BỊ XÂM HẠI</t>
+          <t>Chủ đề: Phòng tránh bị xâm hại</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr"/>
@@ -14593,7 +14593,7 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr"/>
@@ -14628,7 +14628,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr"/>
@@ -14663,7 +14663,7 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr"/>
@@ -14698,7 +14698,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr"/>
@@ -14733,7 +14733,7 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr"/>
@@ -14768,7 +14768,7 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr"/>
@@ -14802,7 +14802,7 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr"/>
@@ -14837,7 +14837,7 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr"/>
@@ -14871,7 +14871,7 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr"/>
@@ -14906,7 +14906,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr"/>
@@ -14940,7 +14940,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr"/>
@@ -14974,7 +14974,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr"/>
@@ -15008,7 +15008,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr"/>
@@ -15043,7 +15043,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr"/>
@@ -15078,7 +15078,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr"/>
@@ -15113,7 +15113,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr"/>
@@ -15148,7 +15148,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr"/>
@@ -15183,7 +15183,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr"/>
@@ -15218,7 +15218,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr"/>
@@ -15253,7 +15253,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr"/>
@@ -15288,7 +15288,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: KẾT NỐI CỘNG ĐỒNG</t>
+          <t>Chủ đề: Kết nối cộng đồng</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr"/>
@@ -15323,7 +15323,7 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TRẢI NGHIỆM NGHỀ TRUYỀN THỐNG</t>
+          <t>Chủ đề: Trải nghiệm nghề truyền thống</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr"/>
@@ -15358,7 +15358,7 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TRẢI NGHIỆM NGHỀ TRUYỀN THỐNG</t>
+          <t>Chủ đề: Trải nghiệm nghề truyền thống</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr"/>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TRẢI NGHIỆM NGHỀ TRUYỀN THỐNG</t>
+          <t>Chủ đề: Trải nghiệm nghề truyền thống</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr"/>
@@ -15428,7 +15428,7 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TRẢI NGHIỆM NGHỀ TRUYỀN THỐNG</t>
+          <t>Chủ đề: Trải nghiệm nghề truyền thống</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr"/>
@@ -15463,7 +15463,7 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TRẢI NGHIỆM NGHỀ TRUYỀN THỐNG</t>
+          <t>Chủ đề: Trải nghiệm nghề truyền thống</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr"/>
@@ -15498,7 +15498,7 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TRẢI NGHIỆM NGHỀ TRUYỀN THỐNG</t>
+          <t>Chủ đề: Trải nghiệm nghề truyền thống</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr"/>
@@ -15533,7 +15533,7 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TRẢI NGHIỆM NGHỀ TRUYỀN THỐNG</t>
+          <t>Chủ đề: Trải nghiệm nghề truyền thống</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr"/>
@@ -15563,7 +15563,7 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TRẢI NGHIỆM NGHỀ TRUYỀN THỐNG</t>
+          <t>Chủ đề: Trải nghiệm nghề truyền thống</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr"/>
@@ -15598,7 +15598,7 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TRẢI NGHIỆM NGHỀ TRUYỀN THỐNG</t>
+          <t>Chủ đề: Trải nghiệm nghề truyền thống</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr"/>
@@ -15633,7 +15633,7 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TRẢI NGHIỆM NGHỀ TRUYỀN THỐNG</t>
+          <t>Chủ đề: Trải nghiệm nghề truyền thống</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr"/>
@@ -15667,7 +15667,7 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TRẢI NGHIỆM NGHỀ TRUYỀN THỐNG</t>
+          <t>Chủ đề: Trải nghiệm nghề truyền thống</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr"/>
@@ -15701,7 +15701,7 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: TRẢI NGHIỆM NGHỀ TRUYỀN THỐNG</t>
+          <t>Chủ đề: Trải nghiệm nghề truyền thống</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr"/>
@@ -22543,7 +22543,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr"/>
@@ -22577,7 +22577,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr"/>
@@ -22603,7 +22603,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr"/>
@@ -22639,7 +22639,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr"/>
@@ -22669,7 +22669,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr"/>
@@ -22704,7 +22704,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr"/>
@@ -22734,7 +22734,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr"/>
@@ -22769,7 +22769,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -22795,7 +22795,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
@@ -22829,7 +22829,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -22859,7 +22859,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
@@ -22894,7 +22894,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr"/>
@@ -22924,7 +22924,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 1: CHẤT</t>
+          <t>Chủ đề 1: Chất</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr"/>
@@ -22954,7 +22954,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr"/>
@@ -22989,7 +22989,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr"/>
@@ -23079,7 +23079,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr"/>
@@ -23113,7 +23113,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr"/>
@@ -23143,7 +23143,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr"/>
@@ -23177,7 +23177,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr"/>
@@ -23207,7 +23207,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr"/>
@@ -23243,7 +23243,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr"/>
@@ -23273,7 +23273,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr"/>
@@ -23308,7 +23308,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr"/>
@@ -23338,7 +23338,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr"/>
@@ -23373,7 +23373,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr"/>
@@ -23399,7 +23399,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 2: NĂNG LƯỢNG</t>
+          <t>Chủ đề 2: Năng lượng</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr"/>
@@ -23429,7 +23429,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr"/>
@@ -23463,7 +23463,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr"/>
@@ -23493,7 +23493,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
@@ -23523,7 +23523,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
@@ -23557,7 +23557,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr"/>
@@ -23587,7 +23587,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr"/>
@@ -23677,7 +23677,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr"/>
@@ -23711,7 +23711,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr"/>
@@ -23741,7 +23741,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 3: THỰC VẬT VÀ ĐỘNG VẬT</t>
+          <t>Chủ đề 3: Thực vật và động vật</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr"/>
@@ -23771,7 +23771,7 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: NẤM</t>
+          <t>Chủ đề 4: Nấm</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr"/>
@@ -23805,7 +23805,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: NẤM</t>
+          <t>Chủ đề 4: Nấm</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr"/>
@@ -23835,7 +23835,7 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: NẤM</t>
+          <t>Chủ đề 4: Nấm</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr"/>
@@ -23869,7 +23869,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: NẤM</t>
+          <t>Chủ đề 4: Nấm</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr"/>
@@ -23899,7 +23899,7 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: NẤM</t>
+          <t>Chủ đề 4: Nấm</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr"/>
@@ -23933,7 +23933,7 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: NẤM</t>
+          <t>Chủ đề 4: Nấm</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr"/>
@@ -23963,7 +23963,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 4: NẤM</t>
+          <t>Chủ đề 4: Nấm</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr"/>
@@ -23993,7 +23993,7 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr"/>
@@ -24028,7 +24028,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr"/>
@@ -24058,7 +24058,7 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr"/>
@@ -24095,7 +24095,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr"/>
@@ -24125,7 +24125,7 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr"/>
@@ -24155,7 +24155,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr"/>
@@ -24190,7 +24190,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr"/>
@@ -24220,7 +24220,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr"/>
@@ -24280,7 +24280,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
@@ -24315,7 +24315,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr"/>
@@ -24345,7 +24345,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
@@ -24379,7 +24379,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr"/>
@@ -24409,7 +24409,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr"/>
@@ -24439,7 +24439,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 5: CON NGƯỜI VÀ SỨC KHOẺ</t>
+          <t>Chủ đề 5: Con người và sức khoẻ</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr"/>
@@ -24465,7 +24465,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr"/>
@@ -24501,7 +24501,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr"/>
@@ -24531,7 +24531,7 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr"/>
@@ -24561,7 +24561,7 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr"/>
@@ -24596,7 +24596,7 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr"/>
@@ -24626,7 +24626,7 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr"/>
@@ -24656,7 +24656,7 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề 6: SINH VẬT VÀ MÔI TRƯỜNG</t>
+          <t>Chủ đề 6: Sinh vật và môi trường</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr"/>
